--- a/pca vactor/pca_vactor.xlsx
+++ b/pca vactor/pca_vactor.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:AP42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,1475 +534,5435 @@
           <t>PC21</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PC22</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>PC23</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>PC24</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>PC25</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>PC26</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>PC27</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>PC28</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>PC29</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>PC30</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>PC31</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>PC32</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>PC33</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>PC34</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>PC35</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>PC36</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>PC37</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>PC38</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>PC39</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>PC40</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>PC41</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>FI-165-1.PV</t>
+          <t>S232-IBAL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.009254016555100353</v>
+        <v>0.005419074253887326</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4279041084015655</v>
+        <v>-0.00423460723270781</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1526494550774683</v>
+        <v>0.151518970027682</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.01806255553532519</v>
+        <v>0.05117709266261582</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01843593382171455</v>
+        <v>0.3371968249846982</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.08081522793792559</v>
+        <v>0.5088833520490567</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3801658035994959</v>
+        <v>-0.1473248395579413</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1729134814019409</v>
+        <v>-0.02588030491050519</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1420014853218014</v>
+        <v>0.188151110018051</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2532958058690293</v>
+        <v>0.005903218211714468</v>
       </c>
       <c r="L2" t="n">
-        <v>0.27169665399096</v>
+        <v>-0.06526248900543981</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02189100833858878</v>
+        <v>0.07379993838503435</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5840143989866966</v>
+        <v>-0.02009945457572305</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2245124321177529</v>
+        <v>-0.1315669170234844</v>
       </c>
       <c r="P2" t="n">
-        <v>0.09702206232131477</v>
+        <v>-0.01520790060635491</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05973504358329724</v>
+        <v>-0.08096531895053555</v>
       </c>
       <c r="R2" t="n">
-        <v>0.09877886649838218</v>
+        <v>0.06335847777707344</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01327469062118001</v>
+        <v>0.01968513462037121</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1866709898255353</v>
+        <v>0.07882275222958668</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.06345871314780581</v>
+        <v>0.04604989326167555</v>
       </c>
       <c r="V2" t="n">
-        <v>-4.206871938363761e-14</v>
+        <v>-0.004114635943831648</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.08243847046796121</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.02563490225280898</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.09206549117318859</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.1570907142788096</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.08781285336952539</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5169989579349744</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4117252054280681</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.07140511462328447</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.05431709921494152</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.02442440525948526</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-0.02973964242535066</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.02148931710613396</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.03146814711322317</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.01638281125562357</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.0164522481998605</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.01690607571376211</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.00332283978406962</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-0.001111968688210814</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.0005627577334233145</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-0.0002526225047308671</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>TI-141-11A.PV</t>
+          <t>S232-NBAL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2348066715542273</v>
+        <v>0.01850890432525967</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1852357686523098</v>
+        <v>-0.04480353040477612</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09574854537464875</v>
+        <v>-0.1341708692787364</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1996247066583529</v>
+        <v>-0.08000724611432232</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1143181461208537</v>
+        <v>-0.3442745999315162</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.04146737677278879</v>
+        <v>-0.4941741353502661</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4672861393135475</v>
+        <v>0.1939210665659016</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4538852062017041</v>
+        <v>0.03269788581997209</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5975230277482857</v>
+        <v>-0.1715537224308397</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06661172042368257</v>
+        <v>0.009834240859981693</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0451373774814466</v>
+        <v>0.05377758100421613</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03072327510586197</v>
+        <v>-0.02920556911612673</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.09704437395069007</v>
+        <v>0.03677163416092009</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1525289387863127</v>
+        <v>0.02194256966854963</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.120614064181969</v>
+        <v>-0.05617934602752585</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.06410698284189278</v>
+        <v>0.1250182961569871</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01578572318513381</v>
+        <v>-0.05563863140324068</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05139689790801603</v>
+        <v>-0.01615148999508613</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05961089105408082</v>
+        <v>-0.06736960549807924</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01195010055628474</v>
+        <v>0.02102618382244859</v>
       </c>
       <c r="V3" t="n">
-        <v>1.291467323483485e-14</v>
+        <v>-0.05749955391683055</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.02981231105240691</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.02338857668605181</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.2445577939058141</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.08590640767150448</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.06846524537066194</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.5311880049856563</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.3757128421080349</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.06376367089445957</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.04364848891795617</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.0133137178173952</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.02404338273637007</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.03892860075680663</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.02610434742615437</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.02203526468202588</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.010210525739978</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.0123034938322705</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.0004201702295952891</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.001893194700379585</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.001880704660339903</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.0001857036506901584</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>TI-141-11B.PV</t>
+          <t>FIC-220-2.PV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2405581807116311</v>
+        <v>0.08644916669688826</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09752065609857147</v>
+        <v>-0.003983611675158624</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1971055866607569</v>
+        <v>-0.1852269563282117</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2596947505932504</v>
+        <v>0.44034702249341</v>
       </c>
       <c r="F4" t="n">
-        <v>0.223314725015495</v>
+        <v>-0.08614980840983705</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.04712582754191082</v>
+        <v>0.1999909375651838</v>
       </c>
       <c r="H4" t="n">
-        <v>0.429497981942852</v>
+        <v>0.05659975860566724</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4754998456861953</v>
+        <v>0.1186571698030389</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1919410603574616</v>
+        <v>-0.07042985973551957</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.36807810103787</v>
+        <v>0.01779919222987058</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2089117754927543</v>
+        <v>-0.0719483066480128</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2668819228262763</v>
+        <v>0.07510082314407736</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2582582505047837</v>
+        <v>-0.01247061293579645</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01407154280560954</v>
+        <v>-0.1336864952172467</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08459301633606399</v>
+        <v>-0.227914441206316</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.03734304967744305</v>
+        <v>0.03656033624123557</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01570766820961568</v>
+        <v>-0.2248657999640326</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.02585291375768667</v>
+        <v>-0.1592213613201808</v>
       </c>
       <c r="T4" t="n">
-        <v>0.009433687762943578</v>
+        <v>-0.1261909539122603</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005264550665533285</v>
+        <v>0.1537053369449482</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.384253897500083e-15</v>
+        <v>0.433753884768522</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.4787464127062865</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.120095702104706</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.1775772628839695</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.1399578935175721</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.07478526397537531</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.01444082214845488</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.03249627032434385</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.02451504814442381</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0.004106441911421678</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.005980416398355025</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.01381372228016783</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.01744476431208838</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.05260925026669887</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.04347226084119232</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.02913383007446446</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.002890882944358385</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.0177633609184045</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.002016111046147498</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.0001926734785433325</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.000580902434788722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>TI-141-11C.PV</t>
+          <t>TI-252-2.PV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2630614508020855</v>
+        <v>0.1013963191031946</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.09416603397312748</v>
+        <v>0.2624693631303304</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2561528913914637</v>
+        <v>0.1876632697966253</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1956587006369761</v>
+        <v>0.1179693369905717</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08132066480936315</v>
+        <v>-0.06233415245511793</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003853614834556138</v>
+        <v>-0.03252976988849408</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004241788549430817</v>
+        <v>0.07749104868222989</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1700515530100323</v>
+        <v>0.01427822077989868</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2825369098657001</v>
+        <v>0.00752294456531578</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4446853284712393</v>
+        <v>-0.04564512815743649</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.06851193720352995</v>
+        <v>-0.0197472485293694</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5177362081038457</v>
+        <v>-0.07833195544348553</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0002295543605036877</v>
+        <v>0.002762751012744358</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4401369515245027</v>
+        <v>-0.06539188525603186</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.05510188188689666</v>
+        <v>0.06880706026625141</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1260766913498965</v>
+        <v>0.06914654954446862</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1213279728560779</v>
+        <v>-0.2735776209111723</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.06568828198608281</v>
+        <v>-0.1691870737470743</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.02148019094164325</v>
+        <v>0.4310939386833466</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.002366037523765568</v>
+        <v>-0.06629759122339625</v>
       </c>
       <c r="V5" t="n">
-        <v>-8.190822819240977e-17</v>
+        <v>-0.2891995066044055</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.04905014808676898</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.6415908516254869</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.1695678447694051</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.03506079887025839</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.09817375533593836</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.01831250913145909</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.06616177020807361</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.001169262469628864</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.02427666038685174</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.01576642509154001</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.02306355639374519</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.002161297345694584</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.001829209859963642</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.02673123609231105</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.003628703722529708</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.01303240248657478</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.006827868808383127</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.001347799931578936</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.005383195063348762</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.001261417889909871</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>TI-134-1.PV</t>
+          <t>FIC-220-3.PV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2898722318260393</v>
+        <v>0.08572670964272583</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0782135742812841</v>
+        <v>-0.2126414525345677</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1339414315832387</v>
+        <v>0.202002928618195</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01320880400067824</v>
+        <v>-0.1797247134960373</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.07825480179487265</v>
+        <v>-0.1129621274482426</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001207681363607799</v>
+        <v>0.01666245560209093</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.245759992898412</v>
+        <v>0.3332639987404574</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07478699959661379</v>
+        <v>0.07954453401484846</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.005550616576212209</v>
+        <v>0.03943229176007744</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07760873275105352</v>
+        <v>-0.05946617832643082</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1238474007917316</v>
+        <v>-0.05193300798275455</v>
       </c>
       <c r="M6" t="n">
-        <v>0.533369428801909</v>
+        <v>0.1793644931859676</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1479015993226278</v>
+        <v>-0.0528963039759829</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1205086815021542</v>
+        <v>-0.06434241129290043</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03883866076641822</v>
+        <v>0.1486041250207892</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.244652640603271</v>
+        <v>-0.1989262761258459</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1506941225329086</v>
+        <v>0.1409758223800404</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3132698458935539</v>
+        <v>0.05252335012000178</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5135942307196075</v>
+        <v>0.03640603180681993</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1770994726951913</v>
+        <v>0.04162160441680296</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.480566209317553e-13</v>
+        <v>0.08960165936458554</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1341137168269047</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.01634243995856763</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.2104205140922254</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.004946809894512664</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.05264917153545277</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.003425369912110685</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.02238211462462593</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.0008796204486356031</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.004531677573219542</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.05043231116998164</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.07016695301617364</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.07627149079892201</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.581922975186446</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0.334404265688052</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.1236126038977346</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.2234533753073928</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.0797168142951007</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.0212237532869303</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.0002444256955852479</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.002031467984160815</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>TI-134-2.PV</t>
+          <t>TI-220-2.PV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2902025567406616</v>
+        <v>0.1452437644224433</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.01556935418563971</v>
+        <v>-0.2044773502482468</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1813690548890075</v>
+        <v>0.1301012855554614</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.05279257990924523</v>
+        <v>0.06776665092837127</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.05694226790809812</v>
+        <v>-0.1029277952100386</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004411522953726684</v>
+        <v>0.1746589592418923</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2556520002101204</v>
+        <v>0.2661774711916687</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04800047909976894</v>
+        <v>0.01226117812888362</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.04621793037615772</v>
+        <v>0.1303813626824089</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06620934338831014</v>
+        <v>-0.1943839460264552</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04682961693831442</v>
+        <v>-0.0484385619915484</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2114474954238038</v>
+        <v>0.05046377792796471</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06169534870269236</v>
+        <v>-0.02862017217619217</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.04683555319697316</v>
+        <v>-0.1293040682337941</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4859590487905076</v>
+        <v>-0.09397636776916453</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02623551621331435</v>
+        <v>0.08795108331850333</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3224266184986893</v>
+        <v>0.0340222386204327</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4869880574938358</v>
+        <v>0.08138286061233106</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.01913440538664944</v>
+        <v>0.165623173182909</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4137448163706041</v>
+        <v>-0.1927657039547002</v>
       </c>
       <c r="V7" t="n">
-        <v>2.048856393034614e-14</v>
+        <v>-0.3773718238741373</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.01747638730089001</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.1524247505454746</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.5518979880724468</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.2908589784936279</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.009804889616309107</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.003157059087781492</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.2408804685550337</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.05610590871241592</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.0249084827619765</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.005290918092432748</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.06709821988886971</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.06465527392661485</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.01747305151803015</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.05031856911752029</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.005114966337694505</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0.08077802167732293</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.03787689200491176</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.0271759283156802</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.003425561733690749</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.0006394439760450325</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>TI-126-4.PV</t>
+          <t>FIC-280-1.PV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2985759844719013</v>
+        <v>-0.006590561334037568</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0381104106679884</v>
+        <v>0.05771656223578439</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.09834692149706278</v>
+        <v>0.3170804857816913</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02736285446899188</v>
+        <v>-0.3802928005947151</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.05711087171909567</v>
+        <v>0.1432134743715022</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03607594072234338</v>
+        <v>-0.02924243162203982</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1548870378405635</v>
+        <v>0.02859214382199246</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.05689850514178182</v>
+        <v>-0.1103398889852539</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01191723598356225</v>
+        <v>-0.00751698303441018</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1289435692403428</v>
+        <v>0.119479991917552</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04832418351578399</v>
+        <v>0.005938892441857206</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2111198252062985</v>
+        <v>0.01527366428172864</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0941232174516602</v>
+        <v>-0.004592045113483703</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1353245434066438</v>
+        <v>-0.17313026232381</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1599928436064965</v>
+        <v>-0.03024121706799865</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1514994028793507</v>
+        <v>0.1826080372542719</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.4192675947483092</v>
+        <v>-0.1910043342546333</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2626833688301178</v>
+        <v>-0.1140718043583801</v>
       </c>
       <c r="T8" t="n">
-        <v>0.611996407267731</v>
+        <v>-0.2745655256138618</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.329338946896543</v>
+        <v>0.05525981459205517</v>
       </c>
       <c r="V8" t="n">
-        <v>1.947349367275656e-13</v>
+        <v>0.05181487559299668</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.1303730308714036</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.1190047670050541</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.2268660931463593</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.274101702960531</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.07630747502384705</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.04716470451112511</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.1697776568315466</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.004982437504005986</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.01418487974123955</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.1714772393000698</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.01967838080361469</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.1671144769975963</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.2112924367800726</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.07180011980729223</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.3539303450457785</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.2790498131303472</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.01967470827129622</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.04008838403594733</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.01031462470148901</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.004205224627804671</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>TI-126-5.PV</t>
+          <t>FIC-223-1.PV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2907608343919674</v>
+        <v>0.06960797642590998</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09900444182116906</v>
+        <v>-0.1610747069809666</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1019958054160441</v>
+        <v>-0.2362505827917974</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.06779542331272162</v>
+        <v>0.2848758367391608</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.03557546719400689</v>
+        <v>-0.1880470571053262</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.03522561000297517</v>
+        <v>0.06362989033333079</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1826146810147699</v>
+        <v>0.1736061837083888</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04691559232558198</v>
+        <v>0.02570185744401989</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08562609515868576</v>
+        <v>0.04994213973375466</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07748230769552782</v>
+        <v>-0.2025988267893006</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1789196896434655</v>
+        <v>-0.05615785885874547</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1024648046392333</v>
+        <v>0.1287645937140542</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04939400746063771</v>
+        <v>-0.04708605319383453</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3096899319906073</v>
+        <v>-0.2298983022611857</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2834282643916355</v>
+        <v>-0.1235583701511501</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2719195711555356</v>
+        <v>0.06209176210364054</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02389684366020591</v>
+        <v>-0.1501540624276196</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.01081881135782707</v>
+        <v>-0.08002899087420667</v>
       </c>
       <c r="T9" t="n">
-        <v>0.136057113956957</v>
+        <v>0.02228004071641828</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7245243363615474</v>
+        <v>-0.06983036974501657</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.635771136115959e-14</v>
+        <v>0.05623946690934505</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5213331331410666</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.06903553446821516</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.2333576113535858</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.2651625687539595</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.01211510131429148</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.1148111085007531</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.07700513372060079</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.06606947099282466</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.004454819546908273</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.1323031421098984</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.01718743032111677</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.1543381675478919</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.1462388626022904</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.08341461940462272</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.2485276045003641</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0.1701061992081911</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.01172887173627826</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.03505236605393859</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.008927656648248562</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.001294228743754381</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>TI-126-6.PV</t>
+          <t>TI-223-1.PV</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2855278081143486</v>
+        <v>0.1158173939576019</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1468525241560398</v>
+        <v>-0.246036175644898</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.003506543409543123</v>
+        <v>-0.004847232050606095</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0114905777082366</v>
+        <v>0.1558192423684487</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.07506481457868756</v>
+        <v>0.01609100935878583</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.07748007199060471</v>
+        <v>0.0006229581399282662</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.133593127259818</v>
+        <v>-0.1317117294620941</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.07117485176162945</v>
+        <v>0.227551566607376</v>
       </c>
       <c r="J10" t="n">
-        <v>0.05917722273051054</v>
+        <v>-0.006187909941290263</v>
       </c>
       <c r="K10" t="n">
-        <v>0.04938626118259013</v>
+        <v>0.1535282824856379</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.03299934232279681</v>
+        <v>0.05061619611099336</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07843010792631934</v>
+        <v>-0.2238867476494456</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1495165017173413</v>
+        <v>0.06293264737388903</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1287642122401868</v>
+        <v>0.423521806026555</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6250580772019448</v>
+        <v>0.1595881845240523</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2189515145249107</v>
+        <v>-0.2202764298714406</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.1006565270963135</v>
+        <v>0.05049905858360729</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5899009564726</v>
+        <v>0.01407337186109658</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0595735514931855</v>
+        <v>0.1134452313189067</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09897053367284299</v>
+        <v>0.03486405791989877</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.743868981749392e-14</v>
+        <v>-0.05274967806636224</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.09948596894849619</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.02606238332078437</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.001492631321957263</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.2345185976667475</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.1578818534265755</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.03387770132703643</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.1314432829209778</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.05461358691479992</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.01781049809730526</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.1223933814233742</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.02028119931633751</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.1566111001928931</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.2496515045974372</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.1360329431902496</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.3899236618304431</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.3028555667931996</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.01075483874378341</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.04689458962304358</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.008452715284827075</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.001227300843308587</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>TI-126-7.PV</t>
+          <t>TI-223-2.PV</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2778611425413582</v>
+        <v>0.1875496237439942</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1722322860347621</v>
+        <v>-0.2311928838658183</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0121211340817568</v>
+        <v>-0.01006131632622613</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005848645080018262</v>
+        <v>0.1273805224695186</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08447273257415552</v>
+        <v>-0.02287304749798906</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.07094695755225931</v>
+        <v>0.0001179517408128376</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1757034442008846</v>
+        <v>-0.06045431600258717</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0336961543842269</v>
+        <v>0.1703106983698172</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1685220531091003</v>
+        <v>-0.003988789817900731</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.03857278465291312</v>
+        <v>0.1504775306454799</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05849236747182887</v>
+        <v>-0.01593116428764448</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.251648300732529</v>
+        <v>-0.1203410336513938</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2498861596586292</v>
+        <v>0.04417193910858492</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1162079052776914</v>
+        <v>0.2679260209793904</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2213958805348878</v>
+        <v>0.07789224285469699</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01077833396689023</v>
+        <v>-0.1987803495157813</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5764589198098093</v>
+        <v>-0.04322291606596265</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4763658199341357</v>
+        <v>-0.04496924211407078</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1028266480251821</v>
+        <v>0.04744329738967121</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2392776777857351</v>
+        <v>-0.0576481120892415</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5549691459466e-14</v>
+        <v>0.0003309193744123351</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.08518837536277631</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.05163946220004845</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.1928426376414392</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.5384394951816629</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.4693971108891682</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.01807060492346937</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.2750806846559689</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.06399635272203703</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.1163870929055618</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.03570542799380858</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.01639064072141185</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1131022701828913</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.05268190555018702</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.02965318224582692</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.1508849122074491</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.06162694974583512</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.004600286079541591</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.01048930983610613</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.0007952774989068793</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.001278215753743833</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>TI-127-1.PV</t>
+          <t>TI-204-1.PV</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1780789208088473</v>
+        <v>0.1610782745071611</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3249937561043187</v>
+        <v>0.234708522902955</v>
       </c>
       <c r="D12" t="n">
-        <v>0.11076985819904</v>
+        <v>-0.1240788152651814</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2308811335184984</v>
+        <v>-0.0144849959267125</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.161286393515469</v>
+        <v>-0.01966185972698676</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1004961137429418</v>
+        <v>-0.052925633394228</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02456579241221935</v>
+        <v>0.02719166993180282</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2185044177498307</v>
+        <v>-0.2296366270678152</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1945023722303144</v>
+        <v>0.003731927485084888</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2802987460521851</v>
+        <v>-0.06388531390783923</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.07022690331783424</v>
+        <v>0.03266742264668361</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1069110907242237</v>
+        <v>-0.0003097265982466516</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1443555237942026</v>
+        <v>0.03706952790827486</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5960209868040671</v>
+        <v>-0.002842569103129925</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.01353670185052687</v>
+        <v>0.00351345141217901</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.02046870025454199</v>
+        <v>-0.2169415417883944</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2280664560773344</v>
+        <v>0.3354857574453866</v>
       </c>
       <c r="S12" t="n">
-        <v>0.03688906875597163</v>
+        <v>0.2026664448817415</v>
       </c>
       <c r="T12" t="n">
-        <v>0.322716114376504</v>
+        <v>0.1968222754202985</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2136997040106167</v>
+        <v>-0.2748049655619521</v>
       </c>
       <c r="V12" t="n">
-        <v>6.249038967511359e-14</v>
+        <v>0.3526665020165958</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.05518117516844894</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.2446679254104239</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.328866536349581</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.08713081874219394</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.1136210090794728</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.0454799593108603</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.01145090489225362</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.08542728132986636</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.0151433052455205</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.3171142438215093</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.1428602333952358</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.2547929982214387</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0.03264507578779039</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0.06624674711361331</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.01163461330704067</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.07841220909922703</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.03760666163243224</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-0.0221629626289706</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.001478671897026316</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.0004158291369115853</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>TI-127-2.PV</t>
+          <t>TI-204-2.PV</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1634495561847817</v>
+        <v>0.01930016311861862</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3648964329042431</v>
+        <v>0.1031097719430907</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1139483255451337</v>
+        <v>-0.188077003956805</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1176201793680392</v>
+        <v>-0.166266051406795</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.09486198210747705</v>
+        <v>0.2427316144676541</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0974793339510588</v>
+        <v>0.006210937535059284</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.04116608735742835</v>
+        <v>0.1958311606298999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09461220443916381</v>
+        <v>0.4426676158549671</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1051711692131096</v>
+        <v>0.1516738483814818</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3241979732831987</v>
+        <v>-0.116815883356544</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1728632310594745</v>
+        <v>0.01754410599736308</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2886232246478198</v>
+        <v>-0.08074465539541884</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1485358425093652</v>
+        <v>0.2266638435113849</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05877214312150214</v>
+        <v>0.00395654194199723</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2919714965604295</v>
+        <v>-0.0444605908462412</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07742389800901285</v>
+        <v>0.08430244431803888</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.5257302345423954</v>
+        <v>-0.08018794596915337</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.005110557331358241</v>
+        <v>0.008524137786418385</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3428740690776778</v>
+        <v>-0.04753026860898412</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2099493089837246</v>
+        <v>-0.4911105081868223</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.653419892442103e-14</v>
+        <v>0.09781684350676328</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.1442550582823171</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.03368933054479532</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.2286039483524804</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.03584383086366861</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.1252728034878244</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.2574131722536475</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.1937288126467141</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.05708914339544247</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.08202248173127184</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.1686816679780749</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.05814033246142535</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.1582225313869903</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0.03112320679049693</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.01406056824609303</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.06864942530390945</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.03462234318412052</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.001900336021881404</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.01813885323201495</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.001705817731082199</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-6.067043902911912e-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>TI-128-3.PV</t>
+          <t>TI-204-3.PV</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07011982080905151</v>
+        <v>0.09892793515719644</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.3256068252844776</v>
+        <v>0.1561516704218508</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1067335963699522</v>
+        <v>-0.2018622886550962</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4690110328142248</v>
+        <v>-0.1688982887744804</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1649061221880825</v>
+        <v>0.2464450060001954</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2305092013325261</v>
+        <v>-0.0313215877406948</v>
       </c>
       <c r="H14" t="n">
-        <v>0.157646309966519</v>
+        <v>0.1595311318614388</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2574500140808059</v>
+        <v>0.3695017179454375</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.279182544402577</v>
+        <v>0.08418404030731294</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1126546594186901</v>
+        <v>-0.1252806519571815</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5490664958458454</v>
+        <v>0.002759132407603907</v>
       </c>
       <c r="M14" t="n">
-        <v>0.04352876362761907</v>
+        <v>-0.005967556300076852</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.293334027404023</v>
+        <v>0.1952089368839238</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.01637872137120265</v>
+        <v>0.008413984150523857</v>
       </c>
       <c r="P14" t="n">
-        <v>0.01317323074205611</v>
+        <v>-0.01242180229190814</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.07198769242870208</v>
+        <v>0.01958391650002907</v>
       </c>
       <c r="R14" t="n">
-        <v>0.003269138089289061</v>
+        <v>0.01782353613428547</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.01428435429955489</v>
+        <v>0.01598352926222242</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.01821791839406813</v>
+        <v>-0.02757260386638474</v>
       </c>
       <c r="U14" t="n">
-        <v>0.004513603034536499</v>
+        <v>0.1190598543546384</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.194812935708482e-15</v>
+        <v>-0.03670568076896095</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.06199016410559673</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.03225350730756868</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.1935144596771125</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.01755989553353475</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.1037050697351788</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.2672099933634887</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.2358858838968285</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.05072430827681556</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.1345599126281136</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.4435519913514449</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.1403279083361103</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.3443590106793599</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.01812837545382314</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.02539059521563573</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.1679062874431421</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.15450963154964</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0.02816380265867052</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.06700993900769509</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.002728385781258005</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.0006029275037682483</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>TI-128-1.PV</t>
+          <t>TIC-204-4.PV</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1959981446931778</v>
+        <v>0.2177296053769597</v>
       </c>
       <c r="C15" t="n">
-        <v>0.07107974533724598</v>
+        <v>0.1613671990408037</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.07253266708281164</v>
+        <v>-0.1309125995306293</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4730199133426025</v>
+        <v>-0.1286019648411168</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2736542631488585</v>
+        <v>0.1235705050711449</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4039738463005243</v>
+        <v>-0.01445244389484391</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2753426911538487</v>
+        <v>0.06887112893854383</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4495937402291598</v>
+        <v>0.1918982921527058</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3001277877570639</v>
+        <v>0.003787276603424715</v>
       </c>
       <c r="K15" t="n">
-        <v>0.06612349505955384</v>
+        <v>-0.07907667020754464</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3044319482295583</v>
+        <v>-0.005496154959007713</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.04975148718794063</v>
+        <v>0.0269872458321976</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1374028986909682</v>
+        <v>0.1224527060324961</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.04719596518036178</v>
+        <v>-0.03991459349516012</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.02329156111837862</v>
+        <v>0.02214229320323921</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.005637930955599848</v>
+        <v>-0.0378387429782041</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.01248692286798242</v>
+        <v>0.03160698847714102</v>
       </c>
       <c r="S15" t="n">
-        <v>0.003716833297653313</v>
+        <v>-0.03348451665014063</v>
       </c>
       <c r="T15" t="n">
-        <v>0.004319425317852009</v>
+        <v>0.0001838385352002672</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.00460394764708216</v>
+        <v>0.5014239550399824</v>
       </c>
       <c r="V15" t="n">
-        <v>3.077610144111356e-15</v>
+        <v>-0.08448518327787827</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1403043414553498</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.01621848208830419</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.0931584652016144</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.1532376528598285</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.1857188772774094</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.1513902802393905</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.08829478664499474</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.05346487196013249</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.05817903720890047</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.4698132325920936</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.1322441294181651</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.2846285760719829</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0.04831677725901855</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.03950017771629791</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.1786580512392934</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.2481715037106935</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.0569900306454773</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.07855349902888621</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.00206440502904599</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.001062227245280128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>H143-O2</t>
+          <t>TI-204-5.PV</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02549053267663286</v>
+        <v>0.2552892189259433</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2434456018667766</v>
+        <v>0.1728735833784845</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5934223199090822</v>
+        <v>-0.06181181049150763</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05042910777168436</v>
+        <v>-0.01476308858864441</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04375976963317459</v>
+        <v>0.02766404974875088</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1858087890161437</v>
+        <v>-0.05724543204218428</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1271669636572297</v>
+        <v>0.02203188026406623</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1805229085735926</v>
+        <v>-0.03186395685069619</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03146459514162248</v>
+        <v>-0.03472193459494888</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5637564838657929</v>
+        <v>-0.02502132306003527</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07871559612891106</v>
+        <v>0.0123759138360981</v>
       </c>
       <c r="M16" t="n">
-        <v>0.263406524486097</v>
+        <v>-0.002209669239283802</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2940626349721291</v>
+        <v>0.0187441680006846</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08427261232133393</v>
+        <v>-0.06030007603628578</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1090552258696283</v>
+        <v>0.01200254196883376</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.01031462313498338</v>
+        <v>-0.1364925703834919</v>
       </c>
       <c r="R16" t="n">
-        <v>0.002224872501989413</v>
+        <v>0.05770743094371352</v>
       </c>
       <c r="S16" t="n">
-        <v>0.006896002144803517</v>
+        <v>-0.0277715327203652</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.009743978437546111</v>
+        <v>0.09202600912701987</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.008911791174884316</v>
+        <v>0.355867964335264</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.836548811869127e-15</v>
+        <v>0.1269850462309522</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.214282512072827</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.02155696494530146</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.02188583965142128</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.006137738294258429</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.2854168972791554</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.3218580048004142</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.4050661260401364</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.1619826592419456</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.07783010409450117</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.2611496727708824</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.2277614260790359</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.1923334266941869</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.08705171294123308</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.1394402758716611</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.0376558019733929</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0.266321693058901</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-0.1687134538429107</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-0.04253486049349924</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0.01509529736774793</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-0.002948978962309392</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>TIC-126-1.PV</t>
+          <t>TI-204-6.PV</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2312794991772132</v>
+        <v>0.2795974647525485</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.2712923591271383</v>
+        <v>0.1023930109842786</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1716677261209226</v>
+        <v>-0.1215531105795356</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01101525863990081</v>
+        <v>-0.00524605955219368</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02602479284540524</v>
+        <v>0.005409349571347497</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.02992562172004011</v>
+        <v>0.02626913193208559</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1135070360014964</v>
+        <v>-0.01748788337972636</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.06899479589571045</v>
+        <v>-0.09271963203635009</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1782459711298155</v>
+        <v>-0.05145341998663778</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.01604078518968639</v>
+        <v>0.004703111539816454</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1870454165995316</v>
+        <v>0.01135482549106693</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02743041464167189</v>
+        <v>0.01506783045641977</v>
       </c>
       <c r="N17" t="n">
-        <v>0.03252607795484081</v>
+        <v>-0.01429299112657406</v>
       </c>
       <c r="O17" t="n">
-        <v>0.09126872206737792</v>
+        <v>-0.04451238462052948</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2040373125784284</v>
+        <v>0.0608852967845061</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.7951398117712378</v>
+        <v>0.02546952797389237</v>
       </c>
       <c r="R17" t="n">
-        <v>0.01554412645157068</v>
+        <v>0.07627131258447101</v>
       </c>
       <c r="S17" t="n">
-        <v>0.07891486903775018</v>
+        <v>0.02960155673782484</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2523293006763851</v>
+        <v>-0.01920926288272276</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0541208995474086</v>
+        <v>0.1425256638580031</v>
       </c>
       <c r="V17" t="n">
-        <v>-6.522441453209901e-14</v>
+        <v>-0.1265319349130036</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.07995180396206167</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.0192055901262343</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.1068007988341313</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.0658151581532274</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.08160178668341428</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.1957708607167922</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.2049952155541846</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.01388233476595527</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.04697040416668227</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.05403694461355794</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.4507456100880062</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.3519770593337488</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.01069636825396086</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.4142655037742236</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.1729554314604729</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.04791399802897503</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.4088369334676775</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-0.1441383524629263</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.01418376521654561</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.003574107730128756</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>TI-126-8.PV</t>
+          <t>TI-204-7.PV</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2512680877549359</v>
+        <v>0.2801643165926636</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1711238484177609</v>
+        <v>0.04920065616421766</v>
       </c>
       <c r="D18" t="n">
-        <v>0.288856969029491</v>
+        <v>-0.152617357837746</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02760938571697973</v>
+        <v>0.03164461439277536</v>
       </c>
       <c r="F18" t="n">
-        <v>0.04609727752900956</v>
+        <v>0.007663999054231266</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08521674646089243</v>
+        <v>0.04382586597291738</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1373266425645667</v>
+        <v>-0.01352023931706174</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.07926251388872547</v>
+        <v>-0.1096624279715931</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2376893669541312</v>
+        <v>-0.03541511878262756</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.11500148142786</v>
+        <v>0.02026976772306777</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1948069160256101</v>
+        <v>0.01199120752538161</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1154212148540476</v>
+        <v>0.01440643283290619</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1096618015277364</v>
+        <v>-0.02124336467286426</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2767736122260837</v>
+        <v>-0.04575536571970613</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1216212745564243</v>
+        <v>0.08494508474324942</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2459552468901268</v>
+        <v>0.05636283545075486</v>
       </c>
       <c r="R18" t="n">
-        <v>0.002616982239682854</v>
+        <v>0.06583305525059269</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.04466510110042919</v>
+        <v>0.04432867995290518</v>
       </c>
       <c r="T18" t="n">
-        <v>0.04406351262238426</v>
+        <v>-0.04985276108722256</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0007090882966130134</v>
+        <v>0.04442514117633808</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7071067811865331</v>
+        <v>-0.2129187489061447</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.2212669138139157</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.06846875602386276</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.1106560308272933</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.157724401953185</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.07661431286630957</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.01369368504565824</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.0007762795125500553</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.01750731666419626</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.005467771971057158</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.1027017741712608</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.05500624315288267</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0.0720865515101221</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-0.01410522241372528</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.04398167771676504</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0.02503124013182304</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.09703266579253385</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.3472371117062277</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.7488989548454373</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.004099274825463283</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.003400060345967908</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>TI-126-2.PV</t>
+          <t>TI-204-8.PV</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.02918951705713821</v>
+        <v>0.2569656931727858</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.03056397341351491</v>
+        <v>-0.02655547968344903</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1964278580052676</v>
+        <v>-0.2001960044326958</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5664972299291932</v>
+        <v>0.08845119791478069</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6824095160689634</v>
+        <v>0.02062899565180328</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3777406717380285</v>
+        <v>0.0702984078896222</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1022149506760905</v>
+        <v>0.01585401072498681</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06125458522336793</v>
+        <v>-0.1123576841317831</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1078912116893021</v>
+        <v>-0.002749358822716177</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01960775907629824</v>
+        <v>0.02555573908130369</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.04876007768364031</v>
+        <v>0.009015155016298605</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.01051890450130339</v>
+        <v>0.02795532204012239</v>
       </c>
       <c r="N19" t="n">
-        <v>0.03844288188052847</v>
+        <v>-0.02159981761413476</v>
       </c>
       <c r="O19" t="n">
-        <v>0.002360373349271204</v>
+        <v>-0.0514326232691882</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0006963171211319251</v>
+        <v>0.1301214053911189</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.01011830751856111</v>
+        <v>0.0940568494517664</v>
       </c>
       <c r="R19" t="n">
-        <v>0.006231954716211725</v>
+        <v>0.05661293557856916</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0006572220703374464</v>
+        <v>0.06542164362333242</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0002126467109147219</v>
+        <v>-0.07898174335641765</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.001114176522842576</v>
+        <v>-0.04629455053101093</v>
       </c>
       <c r="V19" t="n">
-        <v>1.905849225085793e-16</v>
+        <v>-0.3184819476945124</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.33412185089418</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.05565369529876618</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.01219242733904939</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.3455899263194895</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.2614368575100449</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.1820658414345289</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.1865673563823949</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.03931606853069473</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0.1343241890001875</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.02828028276008722</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-0.1280889108128856</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.2139775001372728</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.002568278968381616</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.2082316377623732</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.01472071883611348</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.1722844415270594</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.03915641577671983</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.4374632688479035</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-0.005412683507116617</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-0.00185067754628226</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>TI-126-3.PV</t>
+          <t>TI-204-9.PV</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.114536329640425</v>
+        <v>0.2954127276976869</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2311326518348013</v>
+        <v>-0.03074396408035738</v>
       </c>
       <c r="D20" t="n">
-        <v>0.185041489384374</v>
+        <v>-0.02096609745326274</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.08010278148997485</v>
+        <v>-0.06103510809801527</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5398285809702809</v>
+        <v>0.02333271226909021</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7398299630847197</v>
+        <v>0.0006038633191728888</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.135975450473745</v>
+        <v>-0.0538764228647213</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1776266090664658</v>
+        <v>-0.1448842019092927</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0533285432967382</v>
+        <v>0.003992260153333713</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01121486262101014</v>
+        <v>0.05150296428992612</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00561330182017785</v>
+        <v>0.03471788124344286</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0151778328398472</v>
+        <v>-0.08221001402590647</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.006449895753707767</v>
+        <v>0.006331465382210263</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01901827751426439</v>
+        <v>-0.02938966196436541</v>
       </c>
       <c r="P20" t="n">
-        <v>0.01507704797928244</v>
+        <v>-0.01870196616323942</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.004609511488156015</v>
+        <v>0.08551323375699779</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009593238675691384</v>
+        <v>-0.04206454135321485</v>
       </c>
       <c r="S20" t="n">
-        <v>0.00229708454041308</v>
+        <v>-0.01043704774048857</v>
       </c>
       <c r="T20" t="n">
-        <v>0.004207509132604762</v>
+        <v>-0.03965315661868479</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0002411547914622806</v>
+        <v>-0.1275045639693041</v>
       </c>
       <c r="V20" t="n">
-        <v>8.83651163038727e-16</v>
+        <v>0.04915538137618764</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.04273392903431047</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.1050309013367578</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.1158821733097146</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.1980875360243611</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.2121511412946826</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.01971566420598059</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.05991285004964468</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.05147141538697669</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.03189748574940691</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.0541323106670843</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-0.4257724761693609</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.2071659504534735</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.07644419000494032</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.02210200397957991</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-0.1496426494365542</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>-0.1758627829720455</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.5989800151911011</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.2769006293300719</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.03770435181128293</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-0.005068089935318257</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>TI-126-8.PV.1</t>
+          <t>TI-204-10.PV</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2512680877549358</v>
+        <v>0.2912639624978812</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1711238484177609</v>
+        <v>-0.007776549090755101</v>
       </c>
       <c r="D21" t="n">
-        <v>0.288856969029491</v>
+        <v>-0.08993194622053415</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02760938571697969</v>
+        <v>-0.01549047891486323</v>
       </c>
       <c r="F21" t="n">
-        <v>0.04609727752900963</v>
+        <v>0.01724842631546265</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.08521674646089242</v>
+        <v>0.02046122913117844</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1373266425645671</v>
+        <v>-0.06979039256356158</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.07926251388872552</v>
+        <v>-0.1537982363052332</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2376893669541303</v>
+        <v>-0.01222431530531633</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1150014814278622</v>
+        <v>0.04243608756709401</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1948069160256074</v>
+        <v>0.03198979535013159</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1154212148540394</v>
+        <v>-0.06484626435637972</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1096618015277294</v>
+        <v>-0.007356523884457071</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2767736122260809</v>
+        <v>-0.02052460514824739</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1216212745564319</v>
+        <v>-0.02159703042987439</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.245955246890119</v>
+        <v>0.1093067028197944</v>
       </c>
       <c r="R21" t="n">
-        <v>0.002616982239705856</v>
+        <v>-0.003664763523448766</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.04466510110042873</v>
+        <v>0.02189335909677749</v>
       </c>
       <c r="T21" t="n">
-        <v>0.04406351262201187</v>
+        <v>-0.05786371134559224</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0007090882967293608</v>
+        <v>-0.1363166373654987</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7071067811865616</v>
+        <v>-0.03159517422462026</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.02376109885808028</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.06266742731474678</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.09443154944154682</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.1418099740802291</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.2401560279383163</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.03127474130114125</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.06149283846425625</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.05142864793933417</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-0.01003409890237763</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-0.3004851783252692</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-0.2596573455627283</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-0.1447931294545497</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.04513132841106116</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.1105763726787832</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.4718355848660846</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.4976544731534517</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-0.1670776086583077</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-0.2092554768267507</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-0.02032454331415668</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-0.0006139012776601698</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>FIC-115-3.PV</t>
+          <t>TI-204-11.PV</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1445785847844517</v>
+        <v>0.2898911800291432</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3158062667000247</v>
+        <v>-0.06815472372158948</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3588424189442394</v>
+        <v>0.02091713995785352</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05694707777786735</v>
+        <v>-0.1086966472904412</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.04911760931905511</v>
+        <v>-0.002600181601343969</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001454754567622077</v>
+        <v>0.02614275605117182</v>
       </c>
       <c r="H22" t="n">
-        <v>0.148810143628416</v>
+        <v>-0.0531702445160819</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2814367556148243</v>
+        <v>-0.09973301711358364</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2957036660061346</v>
+        <v>-0.00613076867121662</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1242548831122507</v>
+        <v>0.05794750563905279</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5205377446191303</v>
+        <v>0.0273234101941508</v>
       </c>
       <c r="M22" t="n">
-        <v>0.09661522724840108</v>
+        <v>-0.07501650373266452</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4473324173589167</v>
+        <v>0.008270686217530632</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2029587696734721</v>
+        <v>-0.006486834215388982</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1142669654508483</v>
+        <v>-0.01100636002325998</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.06669301570927305</v>
+        <v>0.08507719279718802</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.02452274305788627</v>
+        <v>-0.07556601502217235</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.03163511323575789</v>
+        <v>-0.0417184702093694</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.002576638257709069</v>
+        <v>-0.08117906429591555</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0007782140398397124</v>
+        <v>-0.07393551680618787</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.403036908659017e-15</v>
+        <v>0.04479203087312977</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.0658906143208</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.09292727967163465</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.179965178257047</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-0.2681976428366815</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.2853834856984842</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.08609909749223082</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.04168433970914212</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-0.0005756066177900991</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.03919900998005556</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.2745650316120106</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.05262452786536052</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>-0.2684247007986696</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>-0.06865333993168704</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>-0.1523611524654819</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>-0.3432432587432762</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>-0.3027793416167963</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-0.4179146122000076</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-0.2722605065184999</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-0.03172715259477989</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.003529336500209371</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>TI-204-12.PV</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.2800787500901892</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.111465623519915</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.05506664616273525</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.1029490717263625</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0111205280581431</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.004348220013935062</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.01596690150179457</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.08838694987691155</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.03171211084489764</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0759457297819809</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.03127596003157121</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.08879050925340039</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.01114189599641754</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.01136036200814694</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.007153917088872656</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.008394387048876717</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-0.07742947424595609</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.04295547383284324</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.06587408110588776</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.1295483388671095</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.1843400681231761</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1397262924929355</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.08356360695619086</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.05072468921559022</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-0.07742848856748578</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.08830999541243559</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-0.04999367853808803</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.1314530948299492</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-0.05853377705514289</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.02472499104211076</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.2896199364158319</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.5005256659051273</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.07085936836298971</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-0.3045461911145147</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>-0.4630378926538621</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.2313397002757765</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>-0.04878789722595978</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.1682662416775944</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.102644277101551</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.01784890219941525</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>-0.001086744155140004</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>TI-204-13.PV</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.2653607418712275</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.1373815933882906</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.09521257164858458</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.1113253712556485</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.02086421298380337</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.002218833885031008</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.02826097167391195</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.06990519965876978</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.03600687843071743</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.08346416876535931</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.02966574751466355</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.0717886429511575</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.0098979767384887</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.03473365195672807</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.01555393641906733</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.01251445803669312</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-0.08904238638172124</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.05486210307682272</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.09459258190640821</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.1047706134690543</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.2337054704235993</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.1239033209012407</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.1813318994486879</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.07331539189486175</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-0.01177772963214509</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-0.2380894318281576</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-0.1781855923142365</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.194049781559255</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-0.0684498260798454</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>-0.01682780939935899</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.08758259774096906</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.1045377935617832</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.385871411991035</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.2005719114707568</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.5126734255320724</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>-0.2288504785969908</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.1019210370632914</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>-0.2512807393275516</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>-0.01934380466138689</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>-0.001347702478288899</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>-6.660329498207571e-05</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>PIC-204-1.PV</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.1234905378327256</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.002375524808850918</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.07549641053883663</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.1373536395205182</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.2163534665429906</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.1086986720565571</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.0446115300838054</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.1198658116911355</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.02930783081024949</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.08066528157046128</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.0212736066399718</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.6390479755355419</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.1839172316395203</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.4674751532698455</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.3068549059015456</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.1079792592308011</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-0.2578228368380857</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.1096745386141859</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.1350694001895836</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.06987993417524484</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.04473231825186396</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.02666023427766723</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.03053136165823259</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.01220696555631169</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-0.007794542645481119</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-0.04548649830928953</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.01327577271008757</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.01095179088657874</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-0.0008348785120512826</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>-0.04891914634037057</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.01733278648378244</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.009293784733719196</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.007494371620734143</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.00678189685098421</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.005982635135785984</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.0061502734671867</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.003605497717571621</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>-0.001121170553005781</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-0.0002846055143425399</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>-0.000292091107843028</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.000122612598840854</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>TI-224-1.PV</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.1031664736448167</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.1110762213503652</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1639867134098898</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1624572375304056</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1927575812381839</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.2800694543907404</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.2908890126230607</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1609253236835845</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.1371519159661132</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.2712597973925799</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.03188433205665494</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1649406127378643</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.07974951525560824</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.1831609049599248</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.09682738972970746</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.08458400493097183</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.1004292372464532</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.07231700708388682</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.0188369336177939</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.05284367524541245</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.02018254754892604</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.07542004560646773</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.0002886900166583621</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.01123176522088418</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-0.008281910285247536</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-0.04382895778194268</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-0.1214464784115413</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.08774196664387088</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.007714767920818014</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.6810545437240069</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-0.0400974681458268</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>-0.05663710365896676</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-0.03795271097420477</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.0003123644402823247</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.001613419976992062</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>-0.003285437626236666</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-0.03142300108218156</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.009111191868648708</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>-0.01290491001466428</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>-0.007112334490708759</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>-0.0006658839702800599</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>FIC-204-1.PV</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.1284569626774503</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.2661504507580457</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.2012030019532676</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.02677221711235788</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.04471431670470312</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.01482406261906851</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.03860729406414141</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1770607785706107</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.02649559025539653</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.04164182619169372</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0149606771942765</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.08611017716140357</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.01176182560064597</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.0009194461663889832</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.05796847447311793</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.04230750537007364</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.2870292095537373</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.1871160071723642</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.1024637090954322</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.1006100885769196</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.04080091206566758</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.1409074123040673</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.007615631104526669</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.09425883246928292</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.03416689903054985</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-0.4407055638902075</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.0689372380256937</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-0.05093793062251807</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-0.01835802824081948</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>-0.1066642328686172</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.1832132824032046</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>-0.2885284574260017</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-0.3054986523348348</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-0.1964100936972798</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-0.1366325655909468</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-0.1765353277753313</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.3587871723325848</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0.1036150543469464</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-0.008833565411957687</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0.003070141782351125</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.0001811622046600028</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>TI-204-14.PV</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.1061900080698143</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.07159839985733886</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.1957468091813605</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.1686880214516949</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.170658007984563</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.2867224909916389</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.2991587569015927</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1693248764049704</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.1238439296552785</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.2752589521963739</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.01234208427119609</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.09549056391746163</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.05638066862951782</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.2027049184970563</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.105606087839579</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.04241773774403165</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.1121415717306148</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.06072181697867566</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.03024093722760683</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.05538652621403854</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.0773583067997887</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-0.006627468653783955</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.004340890107064391</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.002602134028475243</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.006751611696135897</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.1355532123300794</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.1102775450941546</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>-0.08528593238038101</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>-0.006867200511878654</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>-0.6636094855225909</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.02570051094157246</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.1152683989458675</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.08483027648406395</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.02710307866923548</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.01470631045761364</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.0299461770647773</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-0.03086201872666991</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-0.03286958096338001</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0.008008706615778795</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0.007820846109099111</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.000722251768109384</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>FIC-225-1.PV</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.01519311793232543</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.105795131637806</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.1486679869070356</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.07833794886138591</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.1086439823217037</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.04188227113080886</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.04931974371173822</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.2459150941467382</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.03447262464378829</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.163975338591668</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.004559188401099692</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.2405627529298403</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.8807632486893432</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.07313260165070325</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.07601677656445294</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-5.88413694430706e-05</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-0.02689074034702227</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-0.02231027867095961</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.02552229737971707</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.03400552040384136</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.009557252964677151</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-0.04225415731759809</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-0.002492837793818127</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-0.04728206918509666</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.01487000475204222</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-0.000131443332386646</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.00692967547129986</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-0.005823558508827837</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.006769512403091212</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.0008444957902234133</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0.02440065578641227</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>-0.008936215436497622</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.001014605177251936</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>-0.04125665745849225</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.0268201259523338</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.01390241481734293</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>-0.01414376623360958</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>-0.002819060307982925</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0.006245245101258733</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>-0.0003721335140348176</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-1.682222966427383e-05</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>AI-204-1B.PV</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.09301617697165926</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1794428053584506</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.2013620088691252</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.01767883388538873</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.02879812590897672</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.01600383230116187</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.0236377752150776</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.106807262722306</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.09087965298275161</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.1520710074363077</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.01249317329552094</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.1322759660413909</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.1048634038025213</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.04247248463592609</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.7064396595873033</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-0.2708790560037447</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-0.2936674823839242</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-0.249677567032757</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-0.2023546246249012</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-0.1472742099180465</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.004146516055258365</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.0368714306452011</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-0.08371516274617527</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.1682951658451103</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-0.1243437139092023</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.06033848797206174</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.04528489371241882</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>-0.007426914752853261</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.00649748083679918</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.01741099828034559</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>-0.01917874815401196</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.01222476533898584</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.008913645070237342</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.02155070684272823</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.01262528345480168</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.009999582225492172</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>-0.01103288959914027</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>-0.001696224104187863</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.006559426856540189</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>-0.0003508801596199022</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>-0.0005339028529624289</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>FI-226-1A.PV</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.09572337964202461</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.2096107458157689</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.179782528478993</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.1391716384486949</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.1269464255640359</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.03365039068328456</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3460197529668707</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09304719206963938</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.02867853363680355</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.03867372274704308</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.0645376542675738</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.192330735339221</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-0.1390863465178888</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-0.08529881287071775</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.1505819068548828</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-0.2279278479349413</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.1343220968181598</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.03652417040529689</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.03522824716649146</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.102747705462976</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.1324035021483624</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-0.1949239851486392</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.04533528842707488</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-0.1945505733683307</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.02167677344096534</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.07437512014852765</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.006677145075153717</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.04873498650846456</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.01189534024602982</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>-0.02685659923247055</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>-0.01123417945435451</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>-0.1689679548154286</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>-0.005638921771443711</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>-0.5703792549557233</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.2691438784978752</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.1476761950685989</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>-0.1424482733192285</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>-0.01915040893576118</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0.004007220267052897</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>-0.001249993737725322</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.0006153087507730839</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>AI-204-1A.PV</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.0083443797526909</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.06741152249373915</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.03818423950404209</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.06551930109886066</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.03529252127255082</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.02936140459912215</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.008418370183430321</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.2144351870313976</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.2737542945239022</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.7143004435617935</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-0.1275746831549295</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.3794928203525511</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.1309933867667069</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-0.2988155875314462</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.09674629453414178</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-0.04180736019219938</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.03843489538287809</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.03974596218785093</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.08826508358083909</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-0.1636086894522252</v>
+      </c>
+      <c r="V32" t="n">
+        <v>-0.08564354074790383</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.1347834128963492</v>
+      </c>
+      <c r="X32" t="n">
+        <v>-0.03730230877873075</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.04379258025765767</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-0.1021075545632412</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-0.02428340458112491</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>-0.02212617835379332</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-0.01491266131894769</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.001164441809655371</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>-0.01178879758224237</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.004531113549316138</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.0002478347218066996</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>-0.008088092070002748</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.002544296475052692</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>-0.0004426097989244272</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.005748925653142328</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>-0.005773368898127523</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>-0.00247246799305134</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0.000760801127214905</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0.0002790781657685717</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>8.450049064527843e-05</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>n Pressure</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.07619495107740891</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.2375847639454767</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.2199690270269599</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.1786214366855881</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.0189985395734959</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.09813985128352808</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.1479337146829277</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.06337572632945283</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.2436356350854433</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.07173381137008553</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.05652910379152459</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.0003987097099814491</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.03394845635757852</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-0.1765715000828615</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.07195602370533996</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.09906856612856083</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-0.09234571753078685</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-0.03752755490053356</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.3958195177688876</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.09397694742070646</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.1102779545557541</v>
+      </c>
+      <c r="W33" t="n">
+        <v>-0.117999483096032</v>
+      </c>
+      <c r="X33" t="n">
+        <v>-0.06355971351256544</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.02727657837531001</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.02221785291625496</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.006244293377137286</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-0.01580216148152858</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>-0.03348730408182078</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-0.01583932047487704</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.004637441522219814</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.003455983912519102</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.01602699846257657</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>-0.01924479143250281</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.005415766169453922</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.0139434470137528</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>-0.0003187802338873263</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.0008513390702392403</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>-0.009820178477618065</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.001337800933550319</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0.005626627897019406</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>-0.7050255739163374</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>vel Pressure</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.07639336151705191</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.2382241475947028</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.2208989549532589</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.1769164216541484</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.01899468374115955</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.09743853786532042</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.1472682097407959</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.0627246155476899</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.242971944582546</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.07077878194834621</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.05665388727854747</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.0007883007622286528</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.03376145393172951</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-0.1744254909495448</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.0729325190965433</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.09741688516823126</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-0.09040469238617664</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-0.0362959773945488</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.3943401473270281</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.09217261354648405</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.1098742919074544</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-0.1151422411219198</v>
+      </c>
+      <c r="X34" t="n">
+        <v>-0.05933768105519212</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.02618308434093992</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.02048181048396574</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.006266447681727184</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>-0.01565417579505566</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>-0.03288638893841034</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>-0.01474310783550888</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.005154475067618822</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>-0.002606787481819341</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.009203438694957451</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>-0.01152432519962837</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.006255787932378522</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.009031934448796112</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>-0.002462547445101559</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.001952482491041846</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>-0.00343479349626866</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0.0007111564065600629</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>-0.009988773532729193</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.7090052140538512</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>mperature</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.08264144118814383</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.2542715701372694</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.2527364891970624</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.1132843545867348</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.04467113939940242</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.1161257628721453</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.123841514735762</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.03853846373653406</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-0.02136272521877714</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.02896392060859587</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.004258422182014466</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-0.1549265911723742</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.03369377263169286</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-0.03066325662295773</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-0.04819382287625319</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-0.136653677495114</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-0.137180305834417</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-0.1101826933552432</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.2460407647132305</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-0.02903974943833543</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.08531921599147367</v>
+      </c>
+      <c r="W35" t="n">
+        <v>-0.0828194333942682</v>
+      </c>
+      <c r="X35" t="n">
+        <v>-0.4428589705427021</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>-0.00694514406836803</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.09336191468998792</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-0.02335208404531066</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-0.08393916767623055</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.08881645871826313</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>-0.02276472890289535</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.001457685571993628</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>-0.01338826352339429</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.04474464093020067</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>-0.01016077247166605</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>-0.0001034917038091599</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.03066593370466311</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.008266501049096302</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.02027917790995101</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.01827890548626967</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0.001085801460678747</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>-0.6630901052539837</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>-0.00482036743171909</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>int Temperature</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.09758799370337241</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.2689174371853911</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.2447504439364183</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.04211388980663328</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.07751877946146313</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0250846861022728</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0692481394466677</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.04759027025907121</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-0.09682495998072041</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.002637727460963812</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.0117299509119914</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-0.07758101333645365</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-0.002792966373674168</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.08131350908030371</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.07479456396810366</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.09181073994903161</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-0.1250955168410541</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-0.03857885973005023</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.282031541704292</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-0.01035341803477448</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.1686210929267655</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-0.04678559953632443</v>
+      </c>
+      <c r="X36" t="n">
+        <v>-0.4168001972629903</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.006344266795465346</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.1068823106906487</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-0.03222354387229815</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-0.07059733513128208</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.06639630843013926</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>-0.03408082338619928</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.01453416884160812</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>-0.008207734372498348</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.02221512474631059</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>-0.01969220324009508</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.01153801277981541</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.02459052984786897</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.02750686099196314</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.0102446171476691</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>-0.0470743282573195</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>-0.03432110967524241</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0.6900428791386277</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0.01020599747266258</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>ve Humidity</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.05056361171612819</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.07246202501319157</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0138966269404073</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.1608229806911856</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.3008905038465975</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.333249214984444</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-0.1239219248840904</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2104392913216975</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.1854305308846911</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-0.07772234304888261</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-0.0130730087281267</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.1703049215990168</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-0.08513059863311041</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.2669375016785741</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.2924710345295872</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.5435600687568667</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.01907304008296672</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.1654068938089775</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.1191650079543756</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.02872703766029874</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.1978704376179792</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.07453215276774612</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.03183544203531304</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.0499642635412425</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.03708709629196418</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-0.02599530475319412</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.01364120004111887</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>-0.01869711398902782</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>-0.01663743603192009</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>-0.01070064714375746</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>-0.009326214897238332</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>-0.02238390453407991</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.02868303183821597</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.0001283552256140248</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>-0.01060514743002145</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.002238242524160985</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>-0.002173066804239476</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.01469766673959977</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0.01414860426180929</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>-0.2826598404589494</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>-0.003738676566590987</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>peed</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.09031959861008107</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.1430091862911232</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.05206551970506886</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.1542809263270104</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.3794371625508381</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.05392971555431743</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3316826024425713</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.1933668725229558</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-0.1791515310720371</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.03609588981329041</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.02934913220080354</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-0.05691307682018327</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.01397473293921159</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.101812945872863</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.1833401697169055</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.2218457223725301</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.005954747408333299</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.05936633022583408</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.08210278813818857</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.04704103779294511</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.0975582267527208</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.0690499492476726</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.04090046478535161</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.03526151628069368</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.009867228581992273</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.001685144086184713</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-0.01288052128306321</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.1412805316995141</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.6762980312461051</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>-0.0292498163112041</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.06813567179751509</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.0690558436466117</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>-0.03704298564818321</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>-0.008209005567289892</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.002704029350793105</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.00443388999685893</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0.02328637171429039</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>-0.005764586905565134</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0.008487577648673502</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0.001357516961175681</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>-0.0002127751103845747</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>irection</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.04464615846984991</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.1249765282809418</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.1246835367976359</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.226865976053811</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.01731884327923807</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.1815336311348268</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0551702763747703</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-0.00304166758550403</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.4979049183763979</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.1549357225535974</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.05504807115940134</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.1122221079934155</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-0.01116127364031304</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.06607848135258909</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.07397933242680811</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.05811865341726515</v>
+      </c>
+      <c r="R39" t="n">
+        <v>-0.3044703326547727</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.6703272102362631</v>
+      </c>
+      <c r="T39" t="n">
+        <v>-0.1407335823703741</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.1048243396819367</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.04120665138751128</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.02699794782752712</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.02223073149975149</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-0.02488695869866121</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-0.01305843030817964</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.0264632903380626</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.01892280098913345</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>-0.01537987144881734</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>-0.01391283623768573</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.002849983341315651</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.007886470861052156</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.005061439045093967</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>-0.00393680242490051</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>-0.003190748835925714</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>-0.001403386768998624</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>-0.005019153768620221</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.580602171925787e-06</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>-0.0004447473755786535</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0.001553232890154217</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>-0.000447022292719366</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>-8.878221921034915e-05</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>m Gust</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.09190284243748301</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.1345506546219009</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.04123246800146031</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.1612365565359192</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.3837431401971308</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.03952055046043583</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3398209210431388</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.1848516244511198</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-0.2093257973837889</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.03010000601746919</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.062434253452727</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-0.05147270499012612</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-0.01567108325649237</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.09257223356922079</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.1584968497564845</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.2010386238364767</v>
+      </c>
+      <c r="R40" t="n">
+        <v>-0.003014753169025149</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.03419414848265694</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.05151572928662413</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.05694439447558836</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.05262620910197682</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.02812296147407948</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.02278469458590091</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-0.02398860124631168</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-0.04847790487980322</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.05678349961662971</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.06579191218046943</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>-0.1899737262795756</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>-0.6754948117291935</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.02980729151065216</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>-0.04201314901704106</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>-0.04318498812845353</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.04436722879137327</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>-0.01293890096160134</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>-0.01679133397369489</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>-0.02492848639657794</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>-0.00675239826423061</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>-4.040944456406594e-05</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>-0.001587328013628316</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>-0.006103513133252907</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>-0.000719001449550248</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>m Gust Direction</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.04547812901538374</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1105221465706525</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.1152614704522554</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.2212832401268396</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.02144636144891671</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.1601988172078137</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.07416695158791449</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.01847931167764165</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.5064981432193474</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.1704985124148677</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.07447446931552107</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.1713600566622359</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-0.02330756044826722</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.1527209382274306</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.06050903556516197</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.3067944020605354</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.4494739636496061</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-0.4870869780437859</v>
+      </c>
+      <c r="T41" t="n">
+        <v>-0.08465492179381282</v>
+      </c>
+      <c r="U41" t="n">
+        <v>-0.002333690759080246</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.04046664514997858</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.02941703837728262</v>
+      </c>
+      <c r="X41" t="n">
+        <v>-0.001385579944541972</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.0003657132240468455</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-0.005929963174783833</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.01067867490327061</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.004396520948006858</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>-0.009927300459194391</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>-0.006378162923806569</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.002880242442122905</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.00564011238044834</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.002879441549091334</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>-0.001330061862495804</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>-0.001165049106483902</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>-0.0013746695410511</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>-0.001112595738383021</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>-0.001010183684925085</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>-0.002373937727744113</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0.0009356468114548363</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>6.930604312692174e-05</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>6.821571153160452e-06</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>itation</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>-0.02377945617614426</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.01436837524776152</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.03745833122452591</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.02771509518914151</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.04611454044060491</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.141526392952952</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.04430546406951589</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.07467258976591978</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-0.08579114038068952</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.03204995377333153</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.9627825084181991</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.1108414857556136</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-0.008074822122023959</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-0.08116017576123231</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-0.05194520719576134</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>-0.08163293458303227</v>
+      </c>
+      <c r="R42" t="n">
+        <v>-0.01708488508946227</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-0.007047913752737485</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.01183525381021848</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-0.004611737020359931</v>
+      </c>
+      <c r="V42" t="n">
+        <v>-0.02700354303095583</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.006393440766846596</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-0.001642904953930132</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-0.0002059393751227979</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.01954721902328531</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.02726180856587307</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-0.01082973790794049</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.001394382183301571</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.03052561873980713</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>-0.01397736725447323</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>-0.002178081079379491</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.005911109358167836</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.003023064938529521</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>-0.002860953379586645</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>-0.002354503172142877</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>-0.002597748134904808</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0.0009095251303729439</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0.000229386387224038</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>-0.0009411679658413825</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0.002312169456901595</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>-0.0001612741870490958</v>
       </c>
     </row>
   </sheetData>

--- a/pca vactor/pca_vactor.xlsx
+++ b/pca vactor/pca_vactor.xlsx
@@ -642,127 +642,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005419074253887326</v>
+        <v>0.008676391793988419</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.00423460723270781</v>
+        <v>-0.002604402824395259</v>
       </c>
       <c r="D2" t="n">
-        <v>0.151518970027682</v>
+        <v>0.1482103334802914</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05117709266261582</v>
+        <v>0.06160317067073971</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3371968249846982</v>
+        <v>0.3346358668560734</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5088833520490567</v>
+        <v>0.5074510595352233</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1473248395579413</v>
+        <v>-0.1563653632397647</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02588030491050519</v>
+        <v>-0.03291731965554839</v>
       </c>
       <c r="J2" t="n">
-        <v>0.188151110018051</v>
+        <v>0.1870890250496075</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005903218211714468</v>
+        <v>0.003898454548586148</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.06526248900543981</v>
+        <v>-0.06547412557862657</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07379993838503435</v>
+        <v>0.07571054747878037</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.02009945457572305</v>
+        <v>-0.02248219904839123</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1315669170234844</v>
+        <v>-0.1319987395023547</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.01520790060635491</v>
+        <v>-0.01432357363089186</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.08096531895053555</v>
+        <v>-0.07980082776652192</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06335847777707344</v>
+        <v>0.06153576091718817</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01968513462037121</v>
+        <v>0.02071933125922451</v>
       </c>
       <c r="T2" t="n">
-        <v>0.07882275222958668</v>
+        <v>0.07991579963083771</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04604989326167555</v>
+        <v>0.04348802266189607</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.004114635943831648</v>
+        <v>-0.005889641775288974</v>
       </c>
       <c r="W2" t="n">
-        <v>0.08243847046796121</v>
+        <v>0.08398470761094236</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.02563490225280898</v>
+        <v>-0.02413126924175461</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09206549117318859</v>
+        <v>0.09136773625680135</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1570907142788096</v>
+        <v>0.1562758858795636</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.08781285336952539</v>
+        <v>0.08535054157662741</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5169989579349744</v>
+        <v>0.5192068443174469</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.4117252054280681</v>
+        <v>0.4101922612223564</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.07140511462328447</v>
+        <v>-0.0698988231105143</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.05431709921494152</v>
+        <v>0.05447681003650017</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.02442440525948526</v>
+        <v>-0.02294611414423985</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.02973964242535066</v>
+        <v>-0.02995274657534367</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.02148931710613396</v>
+        <v>0.02052797791917766</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.03146814711322317</v>
+        <v>0.03133560396091175</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.01638281125562357</v>
+        <v>0.01619143278463583</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0164522481998605</v>
+        <v>0.01588759132968835</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.01690607571376211</v>
+        <v>0.01837234595900585</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.00332283978406962</v>
+        <v>0.003220936966453845</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.001111968688210814</v>
+        <v>-0.0006626426481786216</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0005627577334233145</v>
+        <v>0.000545540650742695</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.0002526225047308671</v>
+        <v>-0.000251788159777021</v>
       </c>
     </row>
     <row r="3">
@@ -772,127 +772,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01850890432525967</v>
+        <v>0.01544614263762837</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04480353040477612</v>
+        <v>-0.04632169337164813</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1341708692787364</v>
+        <v>-0.1305788748438008</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.08000724611432232</v>
+        <v>-0.09114681872756698</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3442745999315162</v>
+        <v>-0.3402704806250909</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4941741353502661</v>
+        <v>-0.492389437635557</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1939210665659016</v>
+        <v>0.2028130010210604</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03269788581997209</v>
+        <v>0.04028832008580344</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1715537224308397</v>
+        <v>-0.1704821530305412</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009834240859981693</v>
+        <v>0.01192200316687035</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05377758100421613</v>
+        <v>0.05430765186621353</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.02920556911612673</v>
+        <v>-0.03244392832524926</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03677163416092009</v>
+        <v>0.02995979743246931</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02194256966854963</v>
+        <v>0.01920572249465868</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.05617934602752585</v>
+        <v>-0.05724591574766805</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1250182961569871</v>
+        <v>0.1247633587736712</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.05563863140324068</v>
+        <v>-0.05750440947120733</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.01615148999508613</v>
+        <v>-0.0185530084363986</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.06736960549807924</v>
+        <v>-0.06455103145613078</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02102618382244859</v>
+        <v>0.01906952040344459</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.05749955391683055</v>
+        <v>-0.05473055111804387</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.02981231105240691</v>
+        <v>-0.03058354584979956</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.02338857668605181</v>
+        <v>-0.02193741440198849</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2445577939058141</v>
+        <v>0.2450419482268051</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.08590640767150448</v>
+        <v>0.08486822418841897</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.06846524537066194</v>
+        <v>0.06594976650771701</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5311880049856563</v>
+        <v>0.5342679688859839</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.3757128421080349</v>
+        <v>0.37263059810602</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.06376367089445957</v>
+        <v>-0.06117258558080034</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.04364848891795617</v>
+        <v>0.04392906291781553</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0133137178173952</v>
+        <v>-0.01316652330180081</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.02404338273637007</v>
+        <v>-0.02518756753883688</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.03892860075680663</v>
+        <v>0.03824530231325878</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.02610434742615437</v>
+        <v>0.0260391504901096</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.02203526468202588</v>
+        <v>0.02275082994628547</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.010210525739978</v>
+        <v>0.01043076226642948</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0123034938322705</v>
+        <v>0.0146060220871788</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0004201702295952891</v>
+        <v>0.0001991131438659399</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.001893194700379585</v>
+        <v>-0.001178113570392892</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.001880704660339903</v>
+        <v>0.001850984727332308</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0001857036506901584</v>
+        <v>0.0001872219500156669</v>
       </c>
     </row>
     <row r="4">
@@ -902,127 +902,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08644916669688826</v>
+        <v>0.08364652779256831</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.003983611675158624</v>
+        <v>-0.005244174286444654</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1852269563282117</v>
+        <v>-0.1836668842893734</v>
       </c>
       <c r="E4" t="n">
-        <v>0.44034702249341</v>
+        <v>0.4428865575762816</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08614980840983705</v>
+        <v>-0.08871019766331489</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1999909375651838</v>
+        <v>0.1941434931392494</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05659975860566724</v>
+        <v>0.06291048516070975</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1186571698030389</v>
+        <v>0.1263721216408242</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.07042985973551957</v>
+        <v>-0.07020457619688956</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01779919222987058</v>
+        <v>0.02172707186432092</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0719483066480128</v>
+        <v>-0.07066813547218022</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07510082314407736</v>
+        <v>0.07029660326397695</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01247061293579645</v>
+        <v>-0.03943391932790386</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1336864952172467</v>
+        <v>-0.1300598922158369</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.227914441206316</v>
+        <v>-0.2289917903025517</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03656033624123557</v>
+        <v>0.03404175557678341</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2248657999640326</v>
+        <v>-0.2223535823978682</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1592213613201808</v>
+        <v>-0.1666706443346594</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1261909539122603</v>
+        <v>-0.120280030932643</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1537053369449482</v>
+        <v>0.1608516825111126</v>
       </c>
       <c r="V4" t="n">
-        <v>0.433753884768522</v>
+        <v>0.451803953621618</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4787464127062865</v>
+        <v>-0.4580334402252841</v>
       </c>
       <c r="X4" t="n">
-        <v>0.120095702104706</v>
+        <v>0.11886620827398</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1775772628839695</v>
+        <v>0.1758177153183166</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.1399578935175721</v>
+        <v>-0.1411063648503166</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.07478526397537531</v>
+        <v>0.07434308016704463</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01444082214845488</v>
+        <v>0.01496604940024698</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.03249627032434385</v>
+        <v>-0.0327597700134284</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.02451504814442381</v>
+        <v>0.02478482210888229</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.004106441911421678</v>
+        <v>-0.004155341963106888</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.005980416398355025</v>
+        <v>-0.007064381792436861</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.01381372228016783</v>
+        <v>0.013293067922421</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.01744476431208838</v>
+        <v>-0.01632684615876239</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.05260925026669887</v>
+        <v>0.05230778046987047</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.04347226084119232</v>
+        <v>-0.04285702586234928</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.02913383007446446</v>
+        <v>-0.02998656803176663</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.002890882944358385</v>
+        <v>-0.004871610212449263</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0177633609184045</v>
+        <v>0.01788103012994159</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002016111046147498</v>
+        <v>0.001710847936157703</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.0001926734785433325</v>
+        <v>0.0002205956863687107</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.000580902434788722</v>
+        <v>0.0005646943872898928</v>
       </c>
     </row>
     <row r="5">
@@ -1032,127 +1032,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1013963191031946</v>
+        <v>0.1003128820259736</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2624693631303304</v>
+        <v>0.2633490189340719</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1876632697966253</v>
+        <v>0.18628834807122</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1179693369905717</v>
+        <v>0.1169808470913195</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.06233415245511793</v>
+        <v>-0.06191627597111223</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.03252976988849408</v>
+        <v>-0.03406775646427888</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07749104868222989</v>
+        <v>0.08059613625250542</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01427822077989868</v>
+        <v>0.01875575795298511</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00752294456531578</v>
+        <v>0.008117205180886704</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.04564512815743649</v>
+        <v>-0.0430925149343736</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0197472485293694</v>
+        <v>-0.01927154474587484</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07833195544348553</v>
+        <v>-0.08311474126813945</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002762751012744358</v>
+        <v>-0.02159457980553951</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.06539188525603186</v>
+        <v>-0.05974062940524909</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06880706026625141</v>
+        <v>0.069399739231647</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06914654954446862</v>
+        <v>0.06603471206039949</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.2735776209111723</v>
+        <v>-0.2633899881202952</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1691870737470743</v>
+        <v>-0.1723601435187776</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4310939386833466</v>
+        <v>0.4373523592282751</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06629759122339625</v>
+        <v>-0.09109781378812025</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2891995066044055</v>
+        <v>-0.2787982446275381</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.04905014808676898</v>
+        <v>-0.062046359477378</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6415908516254869</v>
+        <v>0.6399956309632742</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1695678447694051</v>
+        <v>-0.1725871716652497</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.03506079887025839</v>
+        <v>-0.03709251347271838</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.09817375533593836</v>
+        <v>0.09867105888641367</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01831250913145909</v>
+        <v>0.01838092686389815</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.06616177020807361</v>
+        <v>0.06706574633628734</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.001169262469628864</v>
+        <v>0.0008983293715135995</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.02427666038685174</v>
+        <v>0.02426266899165151</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01576642509154001</v>
+        <v>-0.01517546998465943</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.02306355639374519</v>
+        <v>-0.02353605785257211</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.002161297345694584</v>
+        <v>0.002117908456760905</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.001829209859963642</v>
+        <v>0.001773707654885982</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.02673123609231105</v>
+        <v>-0.02643569881612165</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.003628703722529708</v>
+        <v>-0.003893871904731961</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.01303240248657478</v>
+        <v>-0.01398583433503874</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.006827868808383127</v>
+        <v>0.007123506861166</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.001347799931578936</v>
+        <v>-0.001770974684555222</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.005383195063348762</v>
+        <v>0.005421525208619602</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.001261417889909871</v>
+        <v>-0.001271251504816661</v>
       </c>
     </row>
     <row r="6">
@@ -1162,127 +1162,127 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08572670964272583</v>
+        <v>0.08729674581888495</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2126414525345677</v>
+        <v>-0.211078959351585</v>
       </c>
       <c r="D6" t="n">
-        <v>0.202002928618195</v>
+        <v>0.2035281720416703</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1797247134960373</v>
+        <v>-0.1849991312605237</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1129621274482426</v>
+        <v>-0.1009492772015385</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01666245560209093</v>
+        <v>0.02096791083744713</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3332639987404574</v>
+        <v>0.3316029531057894</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07954453401484846</v>
+        <v>0.08439530989678848</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03943229176007744</v>
+        <v>0.03955590743249161</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05946617832643082</v>
+        <v>-0.05890206301126334</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.05193300798275455</v>
+        <v>-0.05188971983981053</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1793644931859676</v>
+        <v>0.1815743340941094</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0528963039759829</v>
+        <v>-0.04632802055306803</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.06434241129290043</v>
+        <v>-0.06180060272583655</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1486041250207892</v>
+        <v>0.1502382571451951</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1989262761258459</v>
+        <v>-0.1975943365216529</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1409758223800404</v>
+        <v>0.1410944650837698</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05252335012000178</v>
+        <v>0.05648965567580887</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03640603180681993</v>
+        <v>0.03293260522459695</v>
       </c>
       <c r="U6" t="n">
-        <v>0.04162160441680296</v>
+        <v>0.04485075840797649</v>
       </c>
       <c r="V6" t="n">
-        <v>0.08960165936458554</v>
+        <v>0.09032451873809028</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1341137168269047</v>
+        <v>-0.1340952861700904</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01634243995856763</v>
+        <v>0.01373123980271335</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.2104205140922254</v>
+        <v>-0.2100576889069717</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.004946809894512664</v>
+        <v>-0.004825008331162844</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.05264917153545277</v>
+        <v>0.05301957021635911</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003425369912110685</v>
+        <v>0.003862852537106206</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02238211462462593</v>
+        <v>0.02211802480365634</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0008796204486356031</v>
+        <v>0.0007582340647012033</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.004531677573219542</v>
+        <v>0.004370907487457335</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.05043231116998164</v>
+        <v>-0.05251071792270572</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.07016695301617364</v>
+        <v>0.06693796509455058</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.07627149079892201</v>
+        <v>-0.07121462432954528</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.581922975186446</v>
+        <v>0.5809057894053999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.334404265688052</v>
+        <v>-0.3375370298348501</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.1236126038977346</v>
+        <v>-0.1418849159187142</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.2234533753073928</v>
+        <v>0.2132205968958999</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0797168142951007</v>
+        <v>0.08044940326455707</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.0212237532869303</v>
+        <v>-0.02042835716642019</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0002444256955852479</v>
+        <v>-0.0002712598246460164</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.002031467984160815</v>
+        <v>-0.002095737477105833</v>
       </c>
     </row>
     <row r="7">
@@ -1292,127 +1292,127 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1452437644224433</v>
+        <v>0.1457222333175335</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2044773502482468</v>
+        <v>-0.203536053807534</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1301012855554614</v>
+        <v>0.1321492552707254</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06776665092837127</v>
+        <v>0.06533014684628752</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1029277952100386</v>
+        <v>-0.09584061728938906</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1746589592418923</v>
+        <v>0.1747932776408755</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2661774711916687</v>
+        <v>0.268352114133572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01226117812888362</v>
+        <v>0.0188613766245608</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1303813626824089</v>
+        <v>0.1308959822182506</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1943839460264552</v>
+        <v>-0.1930397849649643</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0484385619915484</v>
+        <v>-0.04881689411770798</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05046377792796471</v>
+        <v>0.04931402466690591</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02862017217619217</v>
+        <v>-0.04485299670322497</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1293040682337941</v>
+        <v>-0.1268481311774216</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.09397636776916453</v>
+        <v>-0.0928920491675341</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.08795108331850333</v>
+        <v>0.08894811759179125</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0340222386204327</v>
+        <v>0.03180444500201694</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08138286061233106</v>
+        <v>0.0833681295967923</v>
       </c>
       <c r="T7" t="n">
-        <v>0.165623173182909</v>
+        <v>0.1650747200971103</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1927657039547002</v>
+        <v>-0.2094129958435353</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3773718238741373</v>
+        <v>-0.3628448373965576</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01747638730089001</v>
+        <v>0.01080716070618182</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1524247505454746</v>
+        <v>-0.1486459485975153</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5518979880724468</v>
+        <v>0.5544937763100714</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.2908589784936279</v>
+        <v>-0.2926700560843478</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.009804889616309107</v>
+        <v>-0.01047894634973665</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003157059087781492</v>
+        <v>0.004729142806511294</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.2408804685550337</v>
+        <v>-0.2436839733197946</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.05610590871241592</v>
+        <v>0.05773273124367769</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0249084827619765</v>
+        <v>0.02476334753735568</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.005290918092432748</v>
+        <v>-0.008543637618574379</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.06709821988886971</v>
+        <v>0.06408103604845468</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.06465527392661485</v>
+        <v>0.06666206616694444</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01747305151803015</v>
+        <v>0.0181100261100889</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.05031856911752029</v>
+        <v>0.05223410282836619</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.005114966337694505</v>
+        <v>0.01084244236296746</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.08077802167732293</v>
+        <v>-0.07817286217671629</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.03787689200491176</v>
+        <v>-0.03837595397507691</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0271759283156802</v>
+        <v>0.0271578462876202</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.003425561733690749</v>
+        <v>0.003407812937502798</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0006394439760450325</v>
+        <v>0.0006520819267368914</v>
       </c>
     </row>
     <row r="8">
@@ -1422,127 +1422,127 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.006590561334037568</v>
+        <v>-0.002414135220951322</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05771656223578439</v>
+        <v>0.06053836189570062</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3170804857816913</v>
+        <v>0.3145436909847188</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3802928005947151</v>
+        <v>-0.3804661181365412</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1432134743715022</v>
+        <v>0.1471422079103753</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.02924243162203982</v>
+        <v>-0.02404612572021171</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02859214382199246</v>
+        <v>0.02226733226862689</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1103398889852539</v>
+        <v>-0.116148125001038</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.00751698303441018</v>
+        <v>-0.007574931818932575</v>
       </c>
       <c r="K8" t="n">
-        <v>0.119479991917552</v>
+        <v>0.1188648194463241</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005938892441857206</v>
+        <v>0.005738146008498308</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01527366428172864</v>
+        <v>0.01577652959724896</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.004592045113483703</v>
+        <v>-0.02034576936363218</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.17313026232381</v>
+        <v>-0.1725124470010008</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.03024121706799865</v>
+        <v>-0.03092768600008567</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1826080372542719</v>
+        <v>0.1834064848792404</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.1910043342546333</v>
+        <v>-0.1976336375110315</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1140718043583801</v>
+        <v>-0.1235129636514571</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2745655256138618</v>
+        <v>-0.2668919183817398</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05525981459205517</v>
+        <v>0.05573171214543085</v>
       </c>
       <c r="V8" t="n">
-        <v>0.05181487559299668</v>
+        <v>0.0600360720008476</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1303730308714036</v>
+        <v>-0.1264267395096331</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1190047670050541</v>
+        <v>0.1209581056526312</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2268660931463593</v>
+        <v>0.2264883311223344</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.274101702960531</v>
+        <v>0.2728784391307147</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.07630747502384705</v>
+        <v>0.0766836538202615</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.04716470451112511</v>
+        <v>-0.04533007770255775</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1697776568315466</v>
+        <v>-0.171458748346158</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.004982437504005986</v>
+        <v>0.006190471624736645</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01418487974123955</v>
+        <v>0.01445717479285195</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1714772393000698</v>
+        <v>0.1690998645721969</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.01967838080361469</v>
+        <v>-0.01532247812226634</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.1671144769975963</v>
+        <v>-0.1684169263571154</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.2112924367800726</v>
+        <v>0.2114841212725148</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.07180011980729223</v>
+        <v>0.064874772916238</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.3539303450457785</v>
+        <v>0.3667759644632117</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.2790498131303472</v>
+        <v>-0.2611382525103502</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.01967470827129622</v>
+        <v>0.02122027165558272</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.04008838403594733</v>
+        <v>0.03940375667290883</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.01031462470148901</v>
+        <v>-0.01034143186917881</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.004205224627804671</v>
+        <v>0.004249320120841474</v>
       </c>
     </row>
     <row r="9">
@@ -1552,127 +1552,127 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06960797642590998</v>
+        <v>0.06848450897968789</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1610747069809666</v>
+        <v>-0.1619651335479233</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2362505827917974</v>
+        <v>-0.2345343787703784</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2848758367391608</v>
+        <v>0.2838724437705758</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1880470571053262</v>
+        <v>-0.1887811476094286</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06362989033333079</v>
+        <v>0.05942257825691359</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1736061837083888</v>
+        <v>0.1839407935423751</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02570185744401989</v>
+        <v>0.03758708454234196</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04994213973375466</v>
+        <v>0.05121191744161981</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2025988267893006</v>
+        <v>-0.197533539665514</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.05615785885874547</v>
+        <v>-0.05521333835704983</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1287645937140542</v>
+        <v>0.1218737244896516</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04708605319383453</v>
+        <v>-0.09019486470581199</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2298983022611857</v>
+        <v>-0.219564654978768</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1235583701511501</v>
+        <v>-0.12274361126641</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06209176210364054</v>
+        <v>0.05774433775858401</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.1501540624276196</v>
+        <v>-0.1413748875331996</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.08002899087420667</v>
+        <v>-0.08074520940235662</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02228004071641828</v>
+        <v>0.02042271508028911</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06983036974501657</v>
+        <v>-0.06245477999442943</v>
       </c>
       <c r="V9" t="n">
-        <v>0.05623946690934505</v>
+        <v>0.03207950291206152</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5213331331410666</v>
+        <v>0.5227842812989004</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.06903553446821516</v>
+        <v>-0.06666801844045889</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.2333576113535858</v>
+        <v>-0.2355417838589172</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2651625687539595</v>
+        <v>0.2674331025061927</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.01211510131429148</v>
+        <v>-0.01155024576672188</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.1148111085007531</v>
+        <v>-0.1164328940019035</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.07700513372060079</v>
+        <v>0.07877683222106156</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.06606947099282466</v>
+        <v>-0.06767378096523144</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.004454819546908273</v>
+        <v>-0.003877891909299436</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1323031421098984</v>
+        <v>0.134985201091059</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01718743032111677</v>
+        <v>0.02408848369045551</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.1543381675478919</v>
+        <v>-0.1565508152668427</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.1462388626022904</v>
+        <v>0.1468299270086774</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.08341461940462272</v>
+        <v>0.07574666684903879</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.2485276045003641</v>
+        <v>0.2564711602686243</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.1701061992081911</v>
+        <v>-0.1609348722094149</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.01172887173627826</v>
+        <v>0.01270176053816174</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.03505236605393859</v>
+        <v>0.03411221562640044</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.008927656648248562</v>
+        <v>-0.008952577231582094</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001294228743754381</v>
+        <v>0.001326821215277511</v>
       </c>
     </row>
     <row r="10">
@@ -1682,127 +1682,127 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1158173939576019</v>
+        <v>0.1153856057703569</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.246036175644898</v>
+        <v>-0.246292647383605</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.004847232050606095</v>
+        <v>-0.002179697334240713</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1558192423684487</v>
+        <v>0.1538639110202807</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01609100935878583</v>
+        <v>0.01676854569903347</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0006229581399282662</v>
+        <v>-0.001505553489362112</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1317117294620941</v>
+        <v>-0.1359669493061239</v>
       </c>
       <c r="I10" t="n">
-        <v>0.227551566607376</v>
+        <v>0.2252218806246442</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.006187909941290263</v>
+        <v>-0.007488070095082671</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1535282824856379</v>
+        <v>0.1516534532982148</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05061619611099336</v>
+        <v>0.05094285094823986</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2238867476494456</v>
+        <v>-0.2215397070325657</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06293264737388903</v>
+        <v>0.1064598406519194</v>
       </c>
       <c r="O10" t="n">
-        <v>0.423521806026555</v>
+        <v>0.4166618051507306</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1595881845240523</v>
+        <v>0.1584404106503317</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2202764298714406</v>
+        <v>-0.2200951690114959</v>
       </c>
       <c r="R10" t="n">
-        <v>0.05049905858360729</v>
+        <v>0.05508867200585448</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01407337186109658</v>
+        <v>0.01718794667472347</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1134452313189067</v>
+        <v>0.1105371403313556</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03486405791989877</v>
+        <v>0.03323629610112686</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.05274967806636224</v>
+        <v>-0.05312280716575226</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.09948596894849619</v>
+        <v>-0.1059318531469452</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02606238332078437</v>
+        <v>0.02437070085378314</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.001492631321957263</v>
+        <v>0.0005513956227169866</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.2345185976667475</v>
+        <v>-0.233960610329571</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.1578818534265755</v>
+        <v>-0.1581214403768386</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.03387770132703643</v>
+        <v>0.03503716289209898</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1314432829209778</v>
+        <v>0.1299001268918453</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.05461358691479992</v>
+        <v>-0.05368456023447211</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.01781049809730526</v>
+        <v>-0.01673723170263614</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1223933814233742</v>
+        <v>0.1222159203800438</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.02028119931633751</v>
+        <v>0.02553964675170894</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.1566111001928931</v>
+        <v>-0.1583668239080896</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.2496515045974372</v>
+        <v>0.2507261098379731</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1360329431902496</v>
+        <v>0.1281716077790271</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.3899236618304431</v>
+        <v>0.4059705632226005</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.3028555667931996</v>
+        <v>-0.2831783511011898</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.01075483874378341</v>
+        <v>0.01209826310547661</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.04689458962304358</v>
+        <v>0.04645432264201338</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.008452715284827075</v>
+        <v>-0.008509853064972503</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.001227300843308587</v>
+        <v>0.001289190809076735</v>
       </c>
     </row>
     <row r="11">
@@ -1812,127 +1812,127 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1875496237439942</v>
+        <v>0.1873856511988281</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2311928838658183</v>
+        <v>-0.2312620134939988</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.01006131632622613</v>
+        <v>-0.008065723983596911</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1273805224695186</v>
+        <v>0.1256413953833418</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.02287304749798906</v>
+        <v>-0.02199764752563403</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001179517408128376</v>
+        <v>-0.001717888929810286</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.06045431600258717</v>
+        <v>-0.06211900204143439</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1703106983698172</v>
+        <v>0.1711450663800637</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.003988789817900731</v>
+        <v>-0.004630890622697661</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1504775306454799</v>
+        <v>0.1504165650648247</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.01593116428764448</v>
+        <v>-0.01541978755132733</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1203410336513938</v>
+        <v>-0.1201661402950865</v>
       </c>
       <c r="N11" t="n">
-        <v>0.04417193910858492</v>
+        <v>0.0691490504403811</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2679260209793904</v>
+        <v>0.2641165446429523</v>
       </c>
       <c r="P11" t="n">
-        <v>0.07789224285469699</v>
+        <v>0.07704066318508332</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1987803495157813</v>
+        <v>-0.1998809103223065</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.04322291606596265</v>
+        <v>-0.03781898772176912</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.04496924211407078</v>
+        <v>-0.0444500827218775</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04744329738967121</v>
+        <v>0.04510193615708272</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0576481120892415</v>
+        <v>-0.05885076755987542</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0003309193744123351</v>
+        <v>0.0006743362402814669</v>
       </c>
       <c r="W11" t="n">
-        <v>0.08518837536277631</v>
+        <v>0.08731946079046206</v>
       </c>
       <c r="X11" t="n">
-        <v>0.05163946220004845</v>
+        <v>0.05518047029282252</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1928426376414392</v>
+        <v>0.1924570159776869</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.5384394951816629</v>
+        <v>0.5362334054362584</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.4693971108891682</v>
+        <v>0.4700255083123699</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.01807060492346937</v>
+        <v>-0.01491085366710223</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.2750806846559689</v>
+        <v>-0.2764507178454397</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.06399635272203703</v>
+        <v>0.06510066448862423</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.1163870929055618</v>
+        <v>0.1153272936486935</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.03570542799380858</v>
+        <v>-0.03847541072869322</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01639064072141185</v>
+        <v>0.01152134660245157</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.1131022701828913</v>
+        <v>0.1147177012181176</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.05268190555018702</v>
+        <v>-0.05269497516885972</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.02965318224582692</v>
+        <v>-0.02461577338434319</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.1508849122074491</v>
+        <v>-0.1531709157832588</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.06162694974583512</v>
+        <v>0.05607805818393725</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.004600286079541591</v>
+        <v>-0.005179778164337686</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.01048930983610613</v>
+        <v>-0.01028126983664166</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0007952774989068793</v>
+        <v>0.0008171695768536749</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.001278215753743833</v>
+        <v>-0.001300482640173712</v>
       </c>
     </row>
     <row r="12">
@@ -1942,127 +1942,127 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1610782745071611</v>
+        <v>0.159323228896374</v>
       </c>
       <c r="C12" t="n">
-        <v>0.234708522902955</v>
+        <v>0.2356803167881464</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1240788152651814</v>
+        <v>-0.1270652106401197</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0144849959267125</v>
+        <v>-0.01177292111508896</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.01966185972698676</v>
+        <v>-0.02501762415394054</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.052925633394228</v>
+        <v>-0.05384343238261198</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02719166993180282</v>
+        <v>0.03354896356766429</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2296366270678152</v>
+        <v>-0.2262926520019613</v>
       </c>
       <c r="J12" t="n">
-        <v>0.003731927485084888</v>
+        <v>0.004969468554204015</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.06388531390783923</v>
+        <v>-0.06320006206902955</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03266742264668361</v>
+        <v>0.03259705110010451</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0003097265982466516</v>
+        <v>-0.004316565393491284</v>
       </c>
       <c r="N12" t="n">
-        <v>0.03706952790827486</v>
+        <v>0.03114976263269194</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.002842569103129925</v>
+        <v>-0.00616041907562901</v>
       </c>
       <c r="P12" t="n">
-        <v>0.00351345141217901</v>
+        <v>0.003736852114052763</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2169415417883944</v>
+        <v>-0.2173325466456158</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3354857574453866</v>
+        <v>0.3421570233065904</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2026664448817415</v>
+        <v>0.2171298862320561</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1968222754202985</v>
+        <v>0.1777165865325041</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2748049655619521</v>
+        <v>-0.2597736548728757</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3526665020165958</v>
+        <v>0.3569151918859336</v>
       </c>
       <c r="W12" t="n">
-        <v>0.05518117516844894</v>
+        <v>0.07205582301234414</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2446679254104239</v>
+        <v>0.2487081061454711</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.328866536349581</v>
+        <v>0.3248893211412504</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.08713081874219394</v>
+        <v>0.08632502948655031</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.1136210090794728</v>
+        <v>-0.1122332689481902</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.0454799593108603</v>
+        <v>-0.04675824709060215</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01145090489225362</v>
+        <v>0.01241767672214671</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.08542728132986636</v>
+        <v>-0.08551339233755577</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.0151433052455205</v>
+        <v>-0.01445820441255796</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.3171142438215093</v>
+        <v>0.3186517022305203</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.1428602333952358</v>
+        <v>-0.1323264098909749</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.2547929982214387</v>
+        <v>-0.2600403120964047</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.03264507578779039</v>
+        <v>-0.03386207637428382</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.06624674711361331</v>
+        <v>-0.07170422060465452</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.01163461330704067</v>
+        <v>0.004110579858056615</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.07841220909922703</v>
+        <v>0.0736228415032029</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.03760666163243224</v>
+        <v>0.03829531704046715</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.0221629626289706</v>
+        <v>-0.0229291979555199</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.001478671897026316</v>
+        <v>-0.00142184404779867</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0004158291369115853</v>
+        <v>0.0003917733077527706</v>
       </c>
     </row>
     <row r="13">
@@ -2072,127 +2072,127 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01930016311861862</v>
+        <v>0.01838580399808467</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1031097719430907</v>
+        <v>0.1030489914495305</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.188077003956805</v>
+        <v>-0.1899843360869115</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.166266051406795</v>
+        <v>-0.1653960890966418</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2427316144676541</v>
+        <v>0.2496120505575402</v>
       </c>
       <c r="G13" t="n">
-        <v>0.006210937535059284</v>
+        <v>0.008459661192014214</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1958311606298999</v>
+        <v>0.1850933592752286</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4426676158549671</v>
+        <v>0.4428097336767607</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1516738483814818</v>
+        <v>0.1491482237149487</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.116815883356544</v>
+        <v>-0.1155434387603551</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01754410599736308</v>
+        <v>0.02064692142576955</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.08074465539541884</v>
+        <v>-0.09483554361432471</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2266638435113849</v>
+        <v>0.2108791141812413</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00395654194199723</v>
+        <v>-0.01742832237328838</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.0444605908462412</v>
+        <v>-0.04732329492763292</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.08430244431803888</v>
+        <v>0.08555703051182108</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.08018794596915337</v>
+        <v>-0.07795903748226772</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008524137786418385</v>
+        <v>0.009322596963163956</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.04753026860898412</v>
+        <v>-0.0574532576297156</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4911105081868223</v>
+        <v>-0.4925176155391816</v>
       </c>
       <c r="V13" t="n">
-        <v>0.09781684350676328</v>
+        <v>0.1235993831048301</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.1442550582823171</v>
+        <v>-0.1297085596829805</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.03368933054479532</v>
+        <v>-0.03379314092447944</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.2286039483524804</v>
+        <v>-0.2312493116581565</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.03584383086366861</v>
+        <v>0.03412775942345405</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.1252728034878244</v>
+        <v>-0.1271764766511229</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.2574131722536475</v>
+        <v>0.2550896023050886</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.1937288126467141</v>
+        <v>-0.1942335192043594</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.05708914339544247</v>
+        <v>0.05744931060998971</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.08202248173127184</v>
+        <v>0.08171870844048157</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1686816679780749</v>
+        <v>0.1702771624853782</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.05814033246142535</v>
+        <v>0.05545304672636964</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.1582225313869903</v>
+        <v>0.1590761131896919</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.03112320679049693</v>
+        <v>-0.03104005186761886</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.01406056824609303</v>
+        <v>0.01199948589742319</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.06864942530390945</v>
+        <v>0.06674406435984613</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.03462234318412052</v>
+        <v>0.03734456547126029</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.001900336021881404</v>
+        <v>0.002091327327981331</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.01813885323201495</v>
+        <v>-0.01774936302901802</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.001705817731082199</v>
+        <v>-0.001710257262893104</v>
       </c>
       <c r="AP13" t="n">
-        <v>-6.067043902911912e-05</v>
+        <v>-5.600810627548929e-05</v>
       </c>
     </row>
     <row r="14">
@@ -2202,127 +2202,127 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09892793515719644</v>
+        <v>0.09665286391790762</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1561516704218508</v>
+        <v>0.1564603940115781</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2018622886550962</v>
+        <v>-0.2038185276014391</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1688982887744804</v>
+        <v>-0.1683741930044921</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2464450060001954</v>
+        <v>0.2525216169679001</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0313215877406948</v>
+        <v>-0.02910526771671257</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1595311318614388</v>
+        <v>0.1494861972995805</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3695017179454375</v>
+        <v>0.3688024760097728</v>
       </c>
       <c r="J14" t="n">
-        <v>0.08418404030731294</v>
+        <v>0.08214060225946065</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1252806519571815</v>
+        <v>-0.1260802708975065</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002759132407603907</v>
+        <v>0.004985617203474206</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.005967556300076852</v>
+        <v>-0.01490801194293818</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1952089368839238</v>
+        <v>0.1982164970144824</v>
       </c>
       <c r="O14" t="n">
-        <v>0.008413984150523857</v>
+        <v>-0.01429391126872759</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.01242180229190814</v>
+        <v>-0.015382293045857</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01958391650002907</v>
+        <v>0.02202220203082546</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01782353613428547</v>
+        <v>0.01121947852546277</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01598352926222242</v>
+        <v>0.0137876778112009</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.02757260386638474</v>
+        <v>-0.02340298077915559</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1190598543546384</v>
+        <v>0.1145184442242198</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.03670568076896095</v>
+        <v>-0.04119797936126253</v>
       </c>
       <c r="W14" t="n">
-        <v>0.06199016410559673</v>
+        <v>0.05851896412109925</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03225350730756868</v>
+        <v>0.03347247180934336</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1935144596771125</v>
+        <v>0.1935427062082457</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.01755989553353475</v>
+        <v>0.01815456870288758</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.1037050697351788</v>
+        <v>0.1046929499983527</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.2672099933634887</v>
+        <v>-0.265279830644243</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.2358858838968285</v>
+        <v>0.2377028818318832</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.05072430827681556</v>
+        <v>-0.05245545879740356</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.1345599126281136</v>
+        <v>-0.1345562094291608</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.4435519913514449</v>
+        <v>-0.4454981900211872</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.1403279083361103</v>
+        <v>-0.1343699021831492</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.3443590106793599</v>
+        <v>-0.3457669786970356</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.01812837545382314</v>
+        <v>0.0182121176110718</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.02539059521563573</v>
+        <v>0.03140745596979203</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.1679062874431421</v>
+        <v>-0.1585688693673821</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.15450963154964</v>
+        <v>-0.1608949130036463</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.02816380265867052</v>
+        <v>-0.02877344894408482</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.06700993900769509</v>
+        <v>0.06510304113523316</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.002728385781258005</v>
+        <v>0.002772523600354214</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.0006029275037682483</v>
+        <v>-0.0006049720848284004</v>
       </c>
     </row>
     <row r="15">
@@ -2332,127 +2332,127 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2177296053769597</v>
+        <v>0.2161261556176206</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1613671990408037</v>
+        <v>0.1630346269630451</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1309125995306293</v>
+        <v>-0.1332373552526056</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1286019648411168</v>
+        <v>-0.1280354183537803</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1235705050711449</v>
+        <v>0.1262829790601394</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.01445244389484391</v>
+        <v>-0.01312547862585279</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06887112893854383</v>
+        <v>0.06410085086402657</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1918982921527058</v>
+        <v>0.1922017719188956</v>
       </c>
       <c r="J15" t="n">
-        <v>0.003787276603424715</v>
+        <v>0.00272890842876796</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.07907667020754464</v>
+        <v>-0.08053254254625634</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.005496154959007713</v>
+        <v>-0.004358428486600897</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0269872458321976</v>
+        <v>0.02268320786834731</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1224527060324961</v>
+        <v>0.1276294133766079</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.03991459349516012</v>
+        <v>-0.05607259299508146</v>
       </c>
       <c r="P15" t="n">
-        <v>0.02214229320323921</v>
+        <v>0.02003757484654081</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.0378387429782041</v>
+        <v>-0.03631299812774949</v>
       </c>
       <c r="R15" t="n">
-        <v>0.03160698847714102</v>
+        <v>0.02296842275007081</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.03348451665014063</v>
+        <v>-0.03841657090711426</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0001838385352002672</v>
+        <v>0.01379919791272783</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5014239550399824</v>
+        <v>0.498826104118178</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.08448518327787827</v>
+        <v>-0.107905820964649</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1403043414553498</v>
+        <v>0.1278645768706491</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.01621848208830419</v>
+        <v>-0.01707850630554562</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0931584652016144</v>
+        <v>0.09539644488473722</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.1532376528598285</v>
+        <v>-0.1516331192910372</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1857188772774094</v>
+        <v>0.1872751870298774</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.1513902802393905</v>
+        <v>-0.1496788488629194</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.08829478664499474</v>
+        <v>0.08773306732668891</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.05346487196013249</v>
+        <v>-0.05249963677407394</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.05817903720890047</v>
+        <v>0.05928522546303589</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.4698132325920936</v>
+        <v>0.4726422645496496</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.1322441294181651</v>
+        <v>0.1301085793655799</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.2846285760719829</v>
+        <v>0.2836113522514302</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.04831677725901855</v>
+        <v>-0.04859484921924155</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.03950017771629791</v>
+        <v>-0.04849789512620441</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.1786580512392934</v>
+        <v>0.1626190573866212</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.2481715037106935</v>
+        <v>0.2518487782534765</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0569900306454773</v>
+        <v>0.05729447966155111</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.07855349902888621</v>
+        <v>-0.07577987842554011</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.00206440502904599</v>
+        <v>0.002000270280716104</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.001062227245280128</v>
+        <v>0.001048962144098905</v>
       </c>
     </row>
     <row r="16">
@@ -2462,127 +2462,127 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2552892189259433</v>
+        <v>0.2542104730036735</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1728735833784845</v>
+        <v>0.1750871187334998</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.06181181049150763</v>
+        <v>-0.06353786965820311</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.01476308858864441</v>
+        <v>-0.01386850717698187</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02766404974875088</v>
+        <v>0.02614897347572866</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.05724543204218428</v>
+        <v>-0.05805466827683966</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02203188026406623</v>
+        <v>0.02304471279978721</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.03186395685069619</v>
+        <v>-0.031150213636529</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.03472193459494888</v>
+        <v>-0.03451606940179821</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.02502132306003527</v>
+        <v>-0.02559673829974419</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0123759138360981</v>
+        <v>0.01234306579456166</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.002209669239283802</v>
+        <v>-0.002823231437466349</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0187441680006846</v>
+        <v>0.01662700193656765</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.06030007603628578</v>
+        <v>-0.06286097711242612</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01200254196883376</v>
+        <v>0.01166064011063258</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1364925703834919</v>
+        <v>-0.1383877139901313</v>
       </c>
       <c r="R16" t="n">
-        <v>0.05770743094371352</v>
+        <v>0.05692252423585198</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0277715327203652</v>
+        <v>-0.02852242374365346</v>
       </c>
       <c r="T16" t="n">
-        <v>0.09202600912701987</v>
+        <v>0.09939260433681056</v>
       </c>
       <c r="U16" t="n">
-        <v>0.355867964335264</v>
+        <v>0.3599083432004054</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1269850462309522</v>
+        <v>0.1088330441409958</v>
       </c>
       <c r="W16" t="n">
-        <v>0.214282512072827</v>
+        <v>0.2168192104413661</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02155696494530146</v>
+        <v>0.02309888942642527</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.02188583965142128</v>
+        <v>-0.02563298242680641</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.006137738294258429</v>
+        <v>-0.005435976075590851</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.2854168972791554</v>
+        <v>-0.2888593474022012</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.3218580048004142</v>
+        <v>0.3159212845920962</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.4050661260401364</v>
+        <v>-0.4030753096906748</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.1619826592419456</v>
+        <v>0.1621039465629337</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.07783010409450117</v>
+        <v>0.074385104919947</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.2611496727708824</v>
+        <v>-0.2637985588948457</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.2277614260790359</v>
+        <v>-0.2427498152442144</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.1923334266941869</v>
+        <v>0.1921279238133311</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.08705171294123308</v>
+        <v>0.08724226990040908</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.1394402758716611</v>
+        <v>-0.1279901700919113</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0376558019733929</v>
+        <v>0.0519820098068249</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.266321693058901</v>
+        <v>-0.2579370696218712</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0.1687134538429107</v>
+        <v>-0.1657286639497811</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.04253486049349924</v>
+        <v>-0.04464510080805802</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01509529736774793</v>
+        <v>-0.01489498168624921</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.002948978962309392</v>
+        <v>-0.002914787892182951</v>
       </c>
     </row>
     <row r="17">
@@ -2592,127 +2592,127 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2795974647525485</v>
+        <v>0.279253642758754</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1023930109842786</v>
+        <v>0.1041528619161521</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1215531105795356</v>
+        <v>-0.1235615378552808</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.00524605955219368</v>
+        <v>-0.003152986792969009</v>
       </c>
       <c r="F17" t="n">
-        <v>0.005409349571347497</v>
+        <v>0.002384488598350414</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02626913193208559</v>
+        <v>0.02588592297954674</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.01748788337972636</v>
+        <v>-0.01590332105525155</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09271963203635009</v>
+        <v>-0.09362985143840229</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.05145341998663778</v>
+        <v>-0.05127938360739709</v>
       </c>
       <c r="K17" t="n">
-        <v>0.004703111539816454</v>
+        <v>0.00400966230792995</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01135482549106693</v>
+        <v>0.01100197928132226</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01506783045641977</v>
+        <v>0.01750744318540448</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.01429299112657406</v>
+        <v>-0.01086177373920307</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.04451238462052948</v>
+        <v>-0.04424839479444199</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0608852967845061</v>
+        <v>0.06128011313905751</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.02546952797389237</v>
+        <v>0.02679043003389704</v>
       </c>
       <c r="R17" t="n">
-        <v>0.07627131258447101</v>
+        <v>0.07090396222869572</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02960155673782484</v>
+        <v>0.02909340621740723</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.01920926288272276</v>
+        <v>-0.01509665526905808</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1425256638580031</v>
+        <v>0.138410937185366</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1265319349130036</v>
+        <v>-0.1279326296808996</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.07995180396206167</v>
+        <v>-0.08772113551628025</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0192055901262343</v>
+        <v>-0.02036518828295917</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.1068007988341313</v>
+        <v>-0.1053324280568866</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0658151581532274</v>
+        <v>0.06479363573327582</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.08160178668341428</v>
+        <v>-0.08104973956821519</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.1957708607167922</v>
+        <v>0.1976045634669445</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.2049952155541846</v>
+        <v>-0.2089578768625574</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.01388233476595527</v>
+        <v>0.01505942248001617</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.04697040416668227</v>
+        <v>0.04739454565727223</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.05403694461355794</v>
+        <v>-0.06155380508965731</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.4507456100880062</v>
+        <v>0.4642389987971532</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.3519770593337488</v>
+        <v>-0.3446491740823664</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.01069636825396086</v>
+        <v>0.01175139933406441</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.4142655037742236</v>
+        <v>0.4100220733003883</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.1729554314604729</v>
+        <v>-0.1651486383156493</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.04791399802897503</v>
+        <v>0.04808233568211243</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.4088369334676775</v>
+        <v>0.4045902520123714</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.1441383524629263</v>
+        <v>-0.1412714063541899</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.01418376521654561</v>
+        <v>0.01405836105262114</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.003574107730128756</v>
+        <v>0.003525306881274726</v>
       </c>
     </row>
     <row r="18">
@@ -2722,127 +2722,127 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2801643165926636</v>
+        <v>0.2800388943291239</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04920065616421766</v>
+        <v>0.05023049928372152</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.152617357837746</v>
+        <v>-0.1545522843800976</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03164461439277536</v>
+        <v>0.03411864591129763</v>
       </c>
       <c r="F18" t="n">
-        <v>0.007663999054231266</v>
+        <v>0.004509615734037531</v>
       </c>
       <c r="G18" t="n">
-        <v>0.04382586597291738</v>
+        <v>0.04320132361441587</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.01352023931706174</v>
+        <v>-0.01158733261946119</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1096624279715931</v>
+        <v>-0.1107788713745782</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.03541511878262756</v>
+        <v>-0.03498357106667985</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02026976772306777</v>
+        <v>0.01973202702390062</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01199120752538161</v>
+        <v>0.01161848772035575</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01440643283290619</v>
+        <v>0.01745020900737378</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.02124336467286426</v>
+        <v>-0.01730631798987881</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.04575536571970613</v>
+        <v>-0.04484451913677398</v>
       </c>
       <c r="P18" t="n">
-        <v>0.08494508474324942</v>
+        <v>0.08582138385438078</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.05636283545075486</v>
+        <v>0.0587217063623302</v>
       </c>
       <c r="R18" t="n">
-        <v>0.06583305525059269</v>
+        <v>0.05912447162717106</v>
       </c>
       <c r="S18" t="n">
-        <v>0.04432867995290518</v>
+        <v>0.0436906217713493</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.04985276108722256</v>
+        <v>-0.0472383625136291</v>
       </c>
       <c r="U18" t="n">
-        <v>0.04442514117633808</v>
+        <v>0.03556664380268224</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2129187489061447</v>
+        <v>-0.2057805629935461</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.2212669138139157</v>
+        <v>-0.2326625883467844</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.06846875602386276</v>
+        <v>-0.07092522270970515</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.1106560308272933</v>
+        <v>-0.1064701479809636</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.157724401953185</v>
+        <v>0.1569239213353319</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.07661431286630957</v>
+        <v>-0.07409472916209239</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.01369368504565824</v>
+        <v>0.01565377164030727</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0007762795125500553</v>
+        <v>-0.001366804351656025</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.01750731666419626</v>
+        <v>-0.01667500695190505</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.005467771971057158</v>
+        <v>-0.004206946566823377</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1027017741712608</v>
+        <v>0.1034295713323342</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.05500624315288267</v>
+        <v>0.05751845622402824</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.0720865515101221</v>
+        <v>-0.07186447006084037</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.01410522241372528</v>
+        <v>-0.01493401889337411</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0.04398167771676504</v>
+        <v>-0.05239420809527137</v>
       </c>
       <c r="AK18" t="n">
-        <v>-0.02503124013182304</v>
+        <v>-0.03497665620185818</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.09703266579253385</v>
+        <v>0.08333127648625861</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.3472371117062277</v>
+        <v>-0.3530872116074997</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.7488989548454373</v>
+        <v>0.7464128454779118</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.004099274825463283</v>
+        <v>0.003340963385765891</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.003400060345967908</v>
+        <v>0.00349463949832656</v>
       </c>
     </row>
     <row r="19">
@@ -2852,127 +2852,127 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2569656931727858</v>
+        <v>0.2565332606894263</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.02655547968344903</v>
+        <v>-0.02673861212938509</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2001960044326958</v>
+        <v>-0.2018729189727065</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08845119791478069</v>
+        <v>0.09146984744382962</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02062899565180328</v>
+        <v>0.01784500242736597</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0702984078896222</v>
+        <v>0.06917213290517853</v>
       </c>
       <c r="H19" t="n">
-        <v>0.01585401072498681</v>
+        <v>0.01846282504428449</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1123576841317831</v>
+        <v>-0.1126509712379539</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.002749358822716177</v>
+        <v>-0.001847821757433561</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02555573908130369</v>
+        <v>0.02533238117920276</v>
       </c>
       <c r="L19" t="n">
-        <v>0.009015155016298605</v>
+        <v>0.00881790580937061</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02795532204012239</v>
+        <v>0.03090164213654779</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.02159981761413476</v>
+        <v>-0.01811915950762122</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0514326232691882</v>
+        <v>-0.05038205019577849</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1301214053911189</v>
+        <v>0.131486115989684</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0940568494517664</v>
+        <v>0.09731755980522135</v>
       </c>
       <c r="R19" t="n">
-        <v>0.05661293557856916</v>
+        <v>0.04866605325962045</v>
       </c>
       <c r="S19" t="n">
-        <v>0.06542164362333242</v>
+        <v>0.06484043267365582</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.07898174335641765</v>
+        <v>-0.07804669678001827</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.04629455053101093</v>
+        <v>-0.05929632839905687</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3184819476945124</v>
+        <v>-0.3057810431684461</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.33412185089418</v>
+        <v>-0.3511836526332703</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.05565369529876618</v>
+        <v>-0.05796786523444283</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.01219242733904939</v>
+        <v>-0.003705031780542836</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.3455899263194895</v>
+        <v>0.346014795644132</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.2614368575100449</v>
+        <v>-0.2580331912742606</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.1820658414345289</v>
+        <v>-0.1787742629836583</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1865673563823949</v>
+        <v>0.1834058891582556</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.03931606853069473</v>
+        <v>-0.03665573751688949</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.1343241890001875</v>
+        <v>-0.1327221179266302</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.02828028276008722</v>
+        <v>0.02504653295965206</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.1280889108128856</v>
+        <v>-0.1393532729009296</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.2139775001372728</v>
+        <v>0.2142916648704894</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.002568278968381616</v>
+        <v>-0.001941605679352502</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.2082316377623732</v>
+        <v>-0.1969593979156815</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.01472071883611348</v>
+        <v>0.02248109571862008</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.1722844415270594</v>
+        <v>-0.1661513579751084</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.03915641577671983</v>
+        <v>0.04565330555382924</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0.4374632688479035</v>
+        <v>-0.4389540480349998</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.005412683507116617</v>
+        <v>-0.004841964537929565</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.00185067754628226</v>
+        <v>-0.001926836698638435</v>
       </c>
     </row>
     <row r="20">
@@ -2982,127 +2982,127 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2954127276976869</v>
+        <v>0.2961886201298442</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.03074396408035738</v>
+        <v>-0.02877569096563223</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.02096609745326274</v>
+        <v>-0.02349631352099126</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.06103510809801527</v>
+        <v>-0.05849388618433142</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02333271226909021</v>
+        <v>0.01928546929876079</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0006038633191728888</v>
+        <v>0.0001468500629399284</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0538764228647213</v>
+        <v>-0.05165665683359662</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1448842019092927</v>
+        <v>-0.144373626279799</v>
       </c>
       <c r="J20" t="n">
-        <v>0.003992260153333713</v>
+        <v>0.004853763201309146</v>
       </c>
       <c r="K20" t="n">
-        <v>0.05150296428992612</v>
+        <v>0.05200985403651925</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03471788124344286</v>
+        <v>0.03459936572747907</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.08221001402590647</v>
+        <v>-0.08436649073081558</v>
       </c>
       <c r="N20" t="n">
-        <v>0.006331465382210263</v>
+        <v>-0.007515118192338775</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.02938966196436541</v>
+        <v>-0.02642316905537664</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.01870196616323942</v>
+        <v>-0.01963332741837528</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.08551323375699779</v>
+        <v>0.08447722956322924</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.04206454135321485</v>
+        <v>-0.04017378453212506</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.01043704774048857</v>
+        <v>-0.01054180194743094</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.03965315661868479</v>
+        <v>-0.04253262633125645</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1275045639693041</v>
+        <v>-0.1240834835723994</v>
       </c>
       <c r="V20" t="n">
-        <v>0.04915538137618764</v>
+        <v>0.05208516551158422</v>
       </c>
       <c r="W20" t="n">
-        <v>0.04273392903431047</v>
+        <v>0.04886631456040192</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1050309013367578</v>
+        <v>-0.1055050761151781</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.1158821733097146</v>
+        <v>-0.1158283597603928</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.1980875360243611</v>
+        <v>-0.1987925520274812</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.2121511412946826</v>
+        <v>0.211408497386348</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.01971566420598059</v>
+        <v>-0.02039996869488598</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.05991285004964468</v>
+        <v>0.06202293020996451</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.05147141538697669</v>
+        <v>0.05123698240462821</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.03189748574940691</v>
+        <v>-0.03243361747571982</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0541323106670843</v>
+        <v>0.05883582687284841</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.4257724761693609</v>
+        <v>-0.4288466242823675</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.2071659504534735</v>
+        <v>0.1949913166449317</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.07644419000494032</v>
+        <v>0.07627477244937897</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.02210200397957991</v>
+        <v>0.03969410879111736</v>
       </c>
       <c r="AK20" t="n">
-        <v>-0.1496426494365542</v>
+        <v>-0.1450469629524457</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.1758627829720455</v>
+        <v>-0.1804165576471151</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.5989800151911011</v>
+        <v>0.5982736915990088</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.2769006293300719</v>
+        <v>0.2789428841345188</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.03770435181128293</v>
+        <v>0.03734182739327553</v>
       </c>
       <c r="AP20" t="n">
-        <v>-0.005068089935318257</v>
+        <v>-0.005042719431928009</v>
       </c>
     </row>
     <row r="21">
@@ -3112,127 +3112,127 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2912639624978812</v>
+        <v>0.2915593444871092</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.007776549090755101</v>
+        <v>-0.006529574253784714</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08993194622053415</v>
+        <v>-0.09188095157413514</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01549047891486323</v>
+        <v>-0.01280518104484775</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01724842631546265</v>
+        <v>0.01261325649283211</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02046122913117844</v>
+        <v>0.01963028043420545</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.06979039256356158</v>
+        <v>-0.06775594782009463</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1537982363052332</v>
+        <v>-0.1547616456188409</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.01222431530531633</v>
+        <v>-0.011399715979236</v>
       </c>
       <c r="K21" t="n">
-        <v>0.04243608756709401</v>
+        <v>0.04239578932890189</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03198979535013159</v>
+        <v>0.03163926177477683</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.06484626435637972</v>
+        <v>-0.06486258125838061</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.007356523884457071</v>
+        <v>-0.01355657230621596</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.02052460514824739</v>
+        <v>-0.01788642465338131</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.02159703042987439</v>
+        <v>-0.02253250838894794</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1093067028197944</v>
+        <v>0.1098243426192342</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.003664763523448766</v>
+        <v>-0.005673566089817138</v>
       </c>
       <c r="S21" t="n">
-        <v>0.02189335909677749</v>
+        <v>0.02164436909148177</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.05786371134559224</v>
+        <v>-0.0598577953777527</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1363166373654987</v>
+        <v>-0.1382839086892785</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.03159517422462026</v>
+        <v>-0.02154182530172052</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.02376109885808028</v>
+        <v>-0.01797555730219122</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.06266742731474678</v>
+        <v>-0.06244913925623626</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.09443154944154682</v>
+        <v>-0.09518742729294642</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.1418099740802291</v>
+        <v>-0.1453190609031587</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.2401560279383163</v>
+        <v>0.2409751370206553</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.03127474130114125</v>
+        <v>0.02839748359953789</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.06149283846425625</v>
+        <v>-0.05640470995723611</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.05142864793933417</v>
+        <v>0.04812326774815066</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.01003409890237763</v>
+        <v>-0.01148770860107208</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.3004851783252692</v>
+        <v>-0.2921747743153736</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.2596573455627283</v>
+        <v>-0.2526149477467131</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.1447931294545497</v>
+        <v>-0.1522096217031169</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.04513132841106116</v>
+        <v>0.04351717677736974</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.1105763726787832</v>
+        <v>0.09431781719357013</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.4718355848660846</v>
+        <v>0.4533893363746539</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.4976544731534517</v>
+        <v>0.5272345008803828</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.1670776086583077</v>
+        <v>-0.1670005666328338</v>
       </c>
       <c r="AN21" t="n">
-        <v>-0.2092554768267507</v>
+        <v>-0.198707243242121</v>
       </c>
       <c r="AO21" t="n">
-        <v>-0.02032454331415668</v>
+        <v>-0.02058088849624824</v>
       </c>
       <c r="AP21" t="n">
-        <v>-0.0006139012776601698</v>
+        <v>-0.000483709101932967</v>
       </c>
     </row>
     <row r="22">
@@ -3242,127 +3242,127 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2898911800291432</v>
+        <v>0.2911000126595674</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.06815472372158948</v>
+        <v>-0.06583843933325323</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02091713995785352</v>
+        <v>0.01825315547280091</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1086966472904412</v>
+        <v>-0.1063626627655311</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.002600181601343969</v>
+        <v>-0.005550036270544714</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02614275605117182</v>
+        <v>0.02645358686106071</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0531702445160819</v>
+        <v>-0.05142945229993045</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.09973301711358364</v>
+        <v>-0.09878235689258354</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.00613076867121662</v>
+        <v>-0.005572632024734742</v>
       </c>
       <c r="K22" t="n">
-        <v>0.05794750563905279</v>
+        <v>0.05857609790733923</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0273234101941508</v>
+        <v>0.02734624902545242</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.07501650373266452</v>
+        <v>-0.07731917990529534</v>
       </c>
       <c r="N22" t="n">
-        <v>0.008270686217530632</v>
+        <v>-0.004321085462998296</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.006486834215388982</v>
+        <v>-0.003545084897224417</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.01100636002325998</v>
+        <v>-0.01206266173521026</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.08507719279718802</v>
+        <v>0.08366912074079415</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.07556601502217235</v>
+        <v>-0.07281724653124651</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0417184702093694</v>
+        <v>-0.04295062556793746</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.08117906429591555</v>
+        <v>-0.08265152113350535</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.07393551680618787</v>
+        <v>-0.06789694378750509</v>
       </c>
       <c r="V22" t="n">
-        <v>0.04479203087312977</v>
+        <v>0.04144458028258641</v>
       </c>
       <c r="W22" t="n">
-        <v>0.0658906143208</v>
+        <v>0.06832671088572365</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.09292727967163465</v>
+        <v>-0.09454003670732267</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.179965178257047</v>
+        <v>-0.1791547563540649</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.2681976428366815</v>
+        <v>-0.2673026418389919</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.2853834856984842</v>
+        <v>0.2832147582942177</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.08609909749223082</v>
+        <v>0.08889034059207801</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.04168433970914212</v>
+        <v>0.0384849220535631</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.0005756066177900991</v>
+        <v>0.002107431682625353</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.03919900998005556</v>
+        <v>0.03959673034732929</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.2745650316120106</v>
+        <v>0.2660882056409947</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.05262452786536052</v>
+        <v>0.05531619886361162</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.2684247007986696</v>
+        <v>-0.2636081330028516</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.06865333993168704</v>
+        <v>-0.06860312770829921</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-0.1523611524654819</v>
+        <v>-0.1483843599626518</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.3432432587432762</v>
+        <v>-0.3305482142652162</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.3027793416167963</v>
+        <v>-0.3263924845297119</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0.4179146122000076</v>
+        <v>-0.4147179540532195</v>
       </c>
       <c r="AN22" t="n">
-        <v>-0.2722605065184999</v>
+        <v>-0.2851871783164446</v>
       </c>
       <c r="AO22" t="n">
-        <v>-0.03172715259477989</v>
+        <v>-0.03084184762249528</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.003529336500209371</v>
+        <v>0.003358804946637991</v>
       </c>
     </row>
     <row r="23">
@@ -3372,127 +3372,127 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2800787500901892</v>
+        <v>0.2816348676690987</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.111465623519915</v>
+        <v>-0.1089519917548564</v>
       </c>
       <c r="D23" t="n">
-        <v>0.05506664616273525</v>
+        <v>0.05259153696803735</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1029490717263625</v>
+        <v>-0.1014504458540818</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0111205280581431</v>
+        <v>0.009456193450955016</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.004348220013935062</v>
+        <v>-0.003982215988249364</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.01596690150179457</v>
+        <v>-0.01467104286514539</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.08838694987691155</v>
+        <v>-0.08670863766629641</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03171211084489764</v>
+        <v>0.03232811861938593</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0759457297819809</v>
+        <v>0.07671587212475031</v>
       </c>
       <c r="L23" t="n">
-        <v>0.03127596003157121</v>
+        <v>0.0313836438808755</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.08879050925340039</v>
+        <v>-0.09176694537136776</v>
       </c>
       <c r="N23" t="n">
-        <v>0.01114189599641754</v>
+        <v>-0.004362932436940076</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.01136036200814694</v>
+        <v>-0.007910599621069058</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.007153917088872656</v>
+        <v>-0.008014768580686166</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.008394387048876717</v>
+        <v>0.006068147187141964</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.07742947424595609</v>
+        <v>-0.07161609276068576</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.04295547383284324</v>
+        <v>-0.04287440654282404</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.06587408110588776</v>
+        <v>-0.070366963014587</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1295483388671095</v>
+        <v>-0.1189647568970565</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1843400681231761</v>
+        <v>0.1809008953413291</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1397262924929355</v>
+        <v>0.1492238030670683</v>
       </c>
       <c r="X23" t="n">
-        <v>0.08356360695619086</v>
+        <v>0.08514233091021833</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.05072468921559022</v>
+        <v>0.0477376399002017</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.07742848856748578</v>
+        <v>-0.07687790819381891</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.08830999541243559</v>
+        <v>-0.08964506894967016</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.04999367853808803</v>
+        <v>-0.05135929403631577</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.1314530948299492</v>
+        <v>0.1330903528203187</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.05853377705514289</v>
+        <v>-0.06013824647754958</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.02472499104211076</v>
+        <v>0.0248897650552458</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.2896199364158319</v>
+        <v>-0.2928625793964659</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.5005256659051273</v>
+        <v>0.491575141511611</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.07085936836298971</v>
+        <v>0.09260365405856039</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.3045461911145147</v>
+        <v>-0.3042004243984261</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.4630378926538621</v>
+        <v>-0.4715400986322815</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.2313397002757765</v>
+        <v>0.2212564966785033</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.04878789722595978</v>
+        <v>-0.05013396556246365</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.1682662416775944</v>
+        <v>0.1706454234986743</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.102644277101551</v>
+        <v>0.1023942137680571</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.01784890219941525</v>
+        <v>0.01783269063846094</v>
       </c>
       <c r="AP23" t="n">
-        <v>-0.001086744155140004</v>
+        <v>-0.001108133174099262</v>
       </c>
     </row>
     <row r="24">
@@ -3502,127 +3502,127 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2653607418712275</v>
+        <v>0.2672007368163927</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1373815933882906</v>
+        <v>-0.1346991363626719</v>
       </c>
       <c r="D24" t="n">
-        <v>0.09521257164858458</v>
+        <v>0.09295352533477803</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1113253712556485</v>
+        <v>-0.1104412359783831</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02086421298380337</v>
+        <v>0.0208959862810331</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.002218833885031008</v>
+        <v>-0.001471691148176742</v>
       </c>
       <c r="H24" t="n">
-        <v>0.02826097167391195</v>
+        <v>0.02870292929594584</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.06990519965876978</v>
+        <v>-0.06801809118438838</v>
       </c>
       <c r="J24" t="n">
-        <v>0.03600687843071743</v>
+        <v>0.03656131545560369</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08346416876535931</v>
+        <v>0.08421659306701514</v>
       </c>
       <c r="L24" t="n">
-        <v>0.02966574751466355</v>
+        <v>0.02987681499072403</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0717886429511575</v>
+        <v>-0.07472647424570224</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0098979767384887</v>
+        <v>-0.006564977208541174</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.03473365195672807</v>
+        <v>-0.03133805294951551</v>
       </c>
       <c r="P24" t="n">
-        <v>0.01555393641906733</v>
+        <v>0.01480423982173913</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.01251445803669312</v>
+        <v>-0.01479128090537452</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.08904238638172124</v>
+        <v>-0.08350641185797049</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.05486210307682272</v>
+        <v>-0.05546750801932618</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.09459258190640821</v>
+        <v>-0.09840041016406355</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1047706134690543</v>
+        <v>-0.09284126260143642</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2337054704235993</v>
+        <v>0.2301673817138981</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1239033209012407</v>
+        <v>0.1348056714898027</v>
       </c>
       <c r="X24" t="n">
-        <v>0.1813318994486879</v>
+        <v>0.1831653845775991</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.07331539189486175</v>
+        <v>0.06900079825837507</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.01177772963214509</v>
+        <v>-0.01137799686454772</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.2380894318281576</v>
+        <v>-0.2381710353620312</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.1781855923142365</v>
+        <v>-0.1813476353433119</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.194049781559255</v>
+        <v>0.198233628981162</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.0684498260798454</v>
+        <v>-0.07194325170184031</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.01682780939935899</v>
+        <v>-0.01624279508509899</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.08758259774096906</v>
+        <v>-0.07867068124378132</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.1045377935617832</v>
+        <v>0.1034026396263736</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.385871411991035</v>
+        <v>0.3804409530889161</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.2005719114707568</v>
+        <v>0.2017838949205333</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.5126734255320724</v>
+        <v>0.5173352577961327</v>
       </c>
       <c r="AK24" t="n">
-        <v>-0.2288504785969908</v>
+        <v>-0.222353703471914</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.1019210370632914</v>
+        <v>0.09935654194678596</v>
       </c>
       <c r="AM24" t="n">
-        <v>-0.2512807393275516</v>
+        <v>-0.2557924318529005</v>
       </c>
       <c r="AN24" t="n">
-        <v>-0.01934380466138689</v>
+        <v>-0.01897950244401962</v>
       </c>
       <c r="AO24" t="n">
-        <v>-0.001347702478288899</v>
+        <v>-0.001358035435811857</v>
       </c>
       <c r="AP24" t="n">
-        <v>-6.660329498207571e-05</v>
+        <v>-5.516422828321014e-05</v>
       </c>
     </row>
     <row r="25">
@@ -3632,127 +3632,127 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1234905378327256</v>
+        <v>0.124199135920545</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.002375524808850918</v>
+        <v>-0.001141209395563301</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.07549641053883663</v>
+        <v>-0.07855544018719664</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1373536395205182</v>
+        <v>-0.1338431550634876</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2163534665429906</v>
+        <v>0.2126485507637556</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1086986720565571</v>
+        <v>-0.1079492118500217</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0446115300838054</v>
+        <v>-0.04690869490421971</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1198658116911355</v>
+        <v>-0.1218023848467007</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.02930783081024949</v>
+        <v>-0.02988316230187641</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.08066528157046128</v>
+        <v>-0.08197907446244956</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0212736066399718</v>
+        <v>-0.02225335698914083</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6390479755355419</v>
+        <v>0.6504852087490958</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1839172316395203</v>
+        <v>-0.1079621826655443</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4674751532698455</v>
+        <v>0.4758377145579975</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.3068549059015456</v>
+        <v>-0.3083712393754071</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.1079792592308011</v>
+        <v>-0.1125879492819301</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.2578228368380857</v>
+        <v>-0.2497819453710662</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1096745386141859</v>
+        <v>-0.113343244156194</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1350694001895836</v>
+        <v>0.1390729470234464</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.06987993417524484</v>
+        <v>-0.08021203104846664</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.04473231825186396</v>
+        <v>-0.03697245223089794</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.02666023427766723</v>
+        <v>-0.02540355868126715</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.03053136165823259</v>
+        <v>-0.03001592728989305</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.01220696555631169</v>
+        <v>0.01217706978878091</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.007794542645481119</v>
+        <v>-0.008176222196204832</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.04548649830928953</v>
+        <v>-0.04554099786228816</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.01327577271008757</v>
+        <v>0.01260394424483286</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.01095179088657874</v>
+        <v>0.01155958103540969</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.0008348785120512826</v>
+        <v>-0.001183869151810743</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.04891914634037057</v>
+        <v>-0.04883667450874233</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.01733278648378244</v>
+        <v>0.0181557945895474</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.009293784733719196</v>
+        <v>0.009668365206953397</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.007494371620734143</v>
+        <v>0.007401078641600127</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.00678189685098421</v>
+        <v>0.006791873402338651</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.005982635135785984</v>
+        <v>0.005353752344418093</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.0061502734671867</v>
+        <v>0.005782795265036649</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.003605497717571621</v>
+        <v>0.003431253986923196</v>
       </c>
       <c r="AM25" t="n">
-        <v>-0.001121170553005781</v>
+        <v>-0.001105958807705762</v>
       </c>
       <c r="AN25" t="n">
-        <v>-0.0002846055143425399</v>
+        <v>-0.000406961705829608</v>
       </c>
       <c r="AO25" t="n">
-        <v>-0.000292091107843028</v>
+        <v>-0.0002778929378818616</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.000122612598840854</v>
+        <v>0.0001226810941174213</v>
       </c>
     </row>
     <row r="26">
@@ -3762,127 +3762,127 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1031664736448167</v>
+        <v>0.1051840982814369</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1110762213503652</v>
+        <v>-0.109264775843026</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1639867134098898</v>
+        <v>0.1624816336237634</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1624572375304056</v>
+        <v>0.162135642244859</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1927575812381839</v>
+        <v>0.1863675590891922</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2800694543907404</v>
+        <v>-0.2830726522335104</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2908890126230607</v>
+        <v>-0.2944623580843971</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1609253236835845</v>
+        <v>0.1546395237349336</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1371519159661132</v>
+        <v>-0.1383872227176103</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2712597973925799</v>
+        <v>-0.2718739267884037</v>
       </c>
       <c r="L26" t="n">
-        <v>0.03188433205665494</v>
+        <v>0.03085627419917185</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1649406127378643</v>
+        <v>0.1680334144705875</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.07974951525560824</v>
+        <v>-0.08800983769104766</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1831609049599248</v>
+        <v>-0.177499896057679</v>
       </c>
       <c r="P26" t="n">
-        <v>0.09682738972970746</v>
+        <v>0.09843833547680528</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.08458400493097183</v>
+        <v>0.08659881909859041</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1004292372464532</v>
+        <v>0.0967446079420242</v>
       </c>
       <c r="S26" t="n">
-        <v>0.07231700708388682</v>
+        <v>0.0743679009691445</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0188369336177939</v>
+        <v>-0.02149540489024731</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.05284367524541245</v>
+        <v>-0.05137886764773306</v>
       </c>
       <c r="V26" t="n">
-        <v>0.02018254754892604</v>
+        <v>0.02537684117407234</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.07542004560646773</v>
+        <v>-0.07351290128696321</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.0002886900166583621</v>
+        <v>-0.0005212399497976606</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.01123176522088418</v>
+        <v>0.01175255444338686</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.008281910285247536</v>
+        <v>-0.008400356860942846</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.04382895778194268</v>
+        <v>-0.04259793287699846</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.1214464784115413</v>
+        <v>-0.1202139584019783</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.08774196664387088</v>
+        <v>0.08615532829517906</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.007714767920818014</v>
+        <v>0.007457180436809222</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.6810545437240069</v>
+        <v>0.6814678249482435</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.0400974681458268</v>
+        <v>-0.04126883778923354</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.05663710365896676</v>
+        <v>-0.05678093742880126</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.03795271097420477</v>
+        <v>-0.03896252021024449</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.0003123644402823247</v>
+        <v>0.0003318914207841997</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.001613419976992062</v>
+        <v>0.002546609051802783</v>
       </c>
       <c r="AK26" t="n">
-        <v>-0.003285437626236666</v>
+        <v>-0.001685706499875334</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.03142300108218156</v>
+        <v>-0.03105786705336533</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.009111191868648708</v>
+        <v>0.009455880101061827</v>
       </c>
       <c r="AN26" t="n">
-        <v>-0.01290491001466428</v>
+        <v>-0.01335527349062546</v>
       </c>
       <c r="AO26" t="n">
-        <v>-0.007112334490708759</v>
+        <v>-0.007093142435050897</v>
       </c>
       <c r="AP26" t="n">
-        <v>-0.0006658839702800599</v>
+        <v>-0.0006795049880476094</v>
       </c>
     </row>
     <row r="27">
@@ -3892,127 +3892,127 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1284569626774503</v>
+        <v>0.1312351337287645</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2661504507580457</v>
+        <v>-0.2639771327525696</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2012030019532676</v>
+        <v>0.2011984522123755</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02677221711235788</v>
+        <v>0.02504982843361957</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04471431670470312</v>
+        <v>0.04728790524893697</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.01482406261906851</v>
+        <v>-0.01527405585175094</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.03860729406414141</v>
+        <v>-0.04246389054340263</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1770607785706107</v>
+        <v>0.1761045246145563</v>
       </c>
       <c r="J27" t="n">
-        <v>0.02649559025539653</v>
+        <v>0.02570293600576824</v>
       </c>
       <c r="K27" t="n">
-        <v>0.04164182619169372</v>
+        <v>0.0418264729660847</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0149606771942765</v>
+        <v>0.01540984145386254</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.08611017716140357</v>
+        <v>-0.08748138545064225</v>
       </c>
       <c r="N27" t="n">
-        <v>0.01176182560064597</v>
+        <v>0.002736354495570917</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0009194461663889832</v>
+        <v>0.00288879627951409</v>
       </c>
       <c r="P27" t="n">
-        <v>0.05796847447311793</v>
+        <v>0.05704230471359768</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.04230750537007364</v>
+        <v>0.0402666313008636</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.2870292095537373</v>
+        <v>-0.2837710355292403</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.1871160071723642</v>
+        <v>-0.1955225020397398</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1024637090954322</v>
+        <v>-0.09340999166677635</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1006100885769196</v>
+        <v>0.09770424198525963</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.04080091206566758</v>
+        <v>-0.047775849242167</v>
       </c>
       <c r="W27" t="n">
-        <v>0.1409074123040673</v>
+        <v>0.1388716768008724</v>
       </c>
       <c r="X27" t="n">
-        <v>0.007615631104526669</v>
+        <v>0.009188463355152261</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.09425883246928292</v>
+        <v>0.0927597318459841</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.03416689903054985</v>
+        <v>0.0350646119417483</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.4407055638902075</v>
+        <v>-0.44129980129486</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.0689372380256937</v>
+        <v>0.0654649137767546</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.05093793062251807</v>
+        <v>-0.049866166409835</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.01835802824081948</v>
+        <v>-0.0186981345415905</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.1066642328686172</v>
+        <v>-0.1069330694619861</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.1832132824032046</v>
+        <v>0.1850220986856609</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.2885284574260017</v>
+        <v>-0.2778687979340175</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.3054986523348348</v>
+        <v>-0.3145038294161065</v>
       </c>
       <c r="AI27" t="n">
-        <v>-0.1964100936972798</v>
+        <v>-0.1991969615116458</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-0.1366325655909468</v>
+        <v>-0.1383328333976767</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0.1765353277753313</v>
+        <v>-0.1974328626083264</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.3587871723325848</v>
+        <v>0.3476996484698278</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.1036150543469464</v>
+        <v>0.1029547651014636</v>
       </c>
       <c r="AN27" t="n">
-        <v>-0.008833565411957687</v>
+        <v>-0.006137268486017463</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.003070141782351125</v>
+        <v>0.002949548936000194</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.0001811622046600028</v>
+        <v>0.00017056993918233</v>
       </c>
     </row>
     <row r="28">
@@ -4022,127 +4022,127 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1061900080698143</v>
+        <v>0.1082130891273325</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.07159839985733886</v>
+        <v>-0.06968670225510297</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1957468091813605</v>
+        <v>0.1939828832412916</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1686880214516949</v>
+        <v>0.1682592077187897</v>
       </c>
       <c r="F28" t="n">
-        <v>0.170658007984563</v>
+        <v>0.1641151440002829</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2867224909916389</v>
+        <v>-0.2898339402781972</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2991587569015927</v>
+        <v>-0.3022204773327773</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1693248764049704</v>
+        <v>0.1635380219361013</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1238439296552785</v>
+        <v>-0.1250728762815971</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.2752589521963739</v>
+        <v>-0.275567238822596</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01234208427119609</v>
+        <v>0.01139866765384255</v>
       </c>
       <c r="M28" t="n">
-        <v>0.09549056391746163</v>
+        <v>0.0969171951037293</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.05638066862951782</v>
+        <v>-0.07137238631002071</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.2027049184970563</v>
+        <v>-0.1981080182773864</v>
       </c>
       <c r="P28" t="n">
-        <v>0.105606087839579</v>
+        <v>0.1072637216734985</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.04241773774403165</v>
+        <v>0.04415225241886549</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1121415717306148</v>
+        <v>0.110567451430284</v>
       </c>
       <c r="S28" t="n">
-        <v>0.06072181697867566</v>
+        <v>0.06379828243138527</v>
       </c>
       <c r="T28" t="n">
-        <v>0.03024093722760683</v>
+        <v>0.02631722819222251</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.05538652621403854</v>
+        <v>-0.05265413847025297</v>
       </c>
       <c r="V28" t="n">
-        <v>0.0773583067997887</v>
+        <v>0.08002936323227537</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.006627468653783955</v>
+        <v>-0.002087720170779083</v>
       </c>
       <c r="X28" t="n">
-        <v>0.004340890107064391</v>
+        <v>0.004748638134910273</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.002602134028475243</v>
+        <v>0.001653449891165138</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.006751611696135897</v>
+        <v>0.006407250713463985</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.1355532123300794</v>
+        <v>0.1343260599540193</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.1102775450941546</v>
+        <v>0.1093733168823415</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.08528593238038101</v>
+        <v>-0.08372621485917743</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.006867200511878654</v>
+        <v>-0.006787120076543412</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.6636094855225909</v>
+        <v>-0.6639599908517245</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.02570051094157246</v>
+        <v>0.02679525357747836</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.1152683989458675</v>
+        <v>0.1139295646540374</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.08483027648406395</v>
+        <v>0.08757896705553875</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.02710307866923548</v>
+        <v>0.02752777107259679</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01470631045761364</v>
+        <v>0.01362088101308802</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.0299461770647773</v>
+        <v>0.031631564267412</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.03086201872666991</v>
+        <v>-0.03022753841957975</v>
       </c>
       <c r="AM28" t="n">
-        <v>-0.03286958096338001</v>
+        <v>-0.03298439039830756</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.008008706615778795</v>
+        <v>0.00763442092166748</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.007820846109099111</v>
+        <v>0.007837128542642235</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.000722251768109384</v>
+        <v>0.0007340618358209022</v>
       </c>
     </row>
     <row r="29">
@@ -4152,127 +4152,127 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01519311793232543</v>
+        <v>-0.007003866217187762</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.105795131637806</v>
+        <v>-0.1057392296628515</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1486679869070356</v>
+        <v>0.1454154744335826</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07833794886138591</v>
+        <v>0.08843190124849039</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1086439823217037</v>
+        <v>-0.1255301657387731</v>
       </c>
       <c r="G29" t="n">
-        <v>0.04188227113080886</v>
+        <v>0.03919885317051408</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.04931974371173822</v>
+        <v>-0.0339861242553348</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2459150941467382</v>
+        <v>-0.2433098698429331</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.03447262464378829</v>
+        <v>-0.03527569721945682</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.163975338591668</v>
+        <v>-0.1650625212549818</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.004559188401099692</v>
+        <v>0.004673469198162688</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2405627529298403</v>
+        <v>0.1988096321117103</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8807632486893432</v>
+        <v>0.893248760689221</v>
       </c>
       <c r="O29" t="n">
-        <v>0.07313260165070325</v>
+        <v>-0.03487962354559829</v>
       </c>
       <c r="P29" t="n">
-        <v>0.07601677656445294</v>
+        <v>0.05944285761168309</v>
       </c>
       <c r="Q29" t="n">
-        <v>-5.88413694430706e-05</v>
+        <v>0.009030926797553854</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.02689074034702227</v>
+        <v>-0.05139821208136922</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.02231027867095961</v>
+        <v>-0.03200195085385811</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.02552229737971707</v>
+        <v>-0.01128570720523414</v>
       </c>
       <c r="U29" t="n">
-        <v>0.03400552040384136</v>
+        <v>0.01386122973375144</v>
       </c>
       <c r="V29" t="n">
-        <v>0.009557252964677151</v>
+        <v>0.02787840579475975</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.04225415731759809</v>
+        <v>-0.03019118722863629</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.002492837793818127</v>
+        <v>-0.0005878850263148453</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.04728206918509666</v>
+        <v>-0.04847135533881151</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.01487000475204222</v>
+        <v>0.01251489534280745</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.000131443332386646</v>
+        <v>-0.0001932494931469168</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.00692967547129986</v>
+        <v>0.003993016844935034</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.005823558508827837</v>
+        <v>-0.0027338488389525</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.006769512403091212</v>
+        <v>0.004843470835675486</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.0008444957902234133</v>
+        <v>0.0005744330308752749</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.02440065578641227</v>
+        <v>-0.02091263255199917</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.008936215436497622</v>
+        <v>-0.007275779402077712</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.001014605177251936</v>
+        <v>0.0002267495468311742</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0.04125665745849225</v>
+        <v>-0.04017470343327714</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.0268201259523338</v>
+        <v>0.02492802068720181</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.01390241481734293</v>
+        <v>0.01362879050850517</v>
       </c>
       <c r="AL29" t="n">
-        <v>-0.01414376623360958</v>
+        <v>-0.01473898307259724</v>
       </c>
       <c r="AM29" t="n">
-        <v>-0.002819060307982925</v>
+        <v>-0.002660675184883653</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.006245245101258733</v>
+        <v>0.005422730027124117</v>
       </c>
       <c r="AO29" t="n">
-        <v>-0.0003721335140348176</v>
+        <v>-0.0003166191214098591</v>
       </c>
       <c r="AP29" t="n">
-        <v>-1.682222966427383e-05</v>
+        <v>-3.727480756320319e-05</v>
       </c>
     </row>
     <row r="30">
@@ -4282,127 +4282,127 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.09301617697165926</v>
+        <v>-0.09474574841043348</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1794428053584506</v>
+        <v>0.177798659951849</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2013620088691252</v>
+        <v>-0.2018127208536958</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01767883388538873</v>
+        <v>0.01986676201377443</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.02879812590897672</v>
+        <v>-0.0326013993605311</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01600383230116187</v>
+        <v>0.01541980994594814</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0236377752150776</v>
+        <v>-0.02003612660766725</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.106807262722306</v>
+        <v>-0.1053991964526232</v>
       </c>
       <c r="J30" t="n">
-        <v>0.09087965298275161</v>
+        <v>0.0911607974361511</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.1520710074363077</v>
+        <v>-0.151474998712748</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01249317329552094</v>
+        <v>0.01183479686415186</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1322759660413909</v>
+        <v>0.1361717183205733</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.1048634038025213</v>
+        <v>-0.098171264032386</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.04247248463592609</v>
+        <v>-0.02813107185732745</v>
       </c>
       <c r="P30" t="n">
-        <v>0.7064396595873033</v>
+        <v>0.7068967971901694</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.2708790560037447</v>
+        <v>-0.2711159301813145</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.2936674823839242</v>
+        <v>-0.287466713304435</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.249677567032757</v>
+        <v>-0.2581715513025163</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.2023546246249012</v>
+        <v>-0.2015492870195892</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.1472742099180465</v>
+        <v>-0.1471214246612924</v>
       </c>
       <c r="V30" t="n">
-        <v>0.004146516055258365</v>
+        <v>0.01125389002917573</v>
       </c>
       <c r="W30" t="n">
-        <v>0.0368714306452011</v>
+        <v>0.04341152942821631</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.08371516274617527</v>
+        <v>-0.08190049225861432</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.1682951658451103</v>
+        <v>0.1680708342211336</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.1243437139092023</v>
+        <v>-0.1258666065011375</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.06033848797206174</v>
+        <v>0.05986681670736654</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.04528489371241882</v>
+        <v>0.04549818772829765</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.007426914752853261</v>
+        <v>-0.007347196692897121</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.00649748083679918</v>
+        <v>0.00650458980356157</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.01741099828034559</v>
+        <v>0.0173384865015709</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.01917874815401196</v>
+        <v>-0.01910248430600544</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.01222476533898584</v>
+        <v>0.01201639064760652</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.008913645070237342</v>
+        <v>0.009221253720247928</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.02155070684272823</v>
+        <v>0.0216407874611619</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.01262528345480168</v>
+        <v>0.01246980744129581</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.009999582225492172</v>
+        <v>0.01067947103030105</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.01103288959914027</v>
+        <v>-0.01034604647125208</v>
       </c>
       <c r="AM30" t="n">
-        <v>-0.001696224104187863</v>
+        <v>-0.001789843638776456</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.006559426856540189</v>
+        <v>0.006604525630272428</v>
       </c>
       <c r="AO30" t="n">
-        <v>-0.0003508801596199022</v>
+        <v>-0.0003501031521691064</v>
       </c>
       <c r="AP30" t="n">
-        <v>-0.0005339028529624289</v>
+        <v>-0.0005360217654096998</v>
       </c>
     </row>
     <row r="31">
@@ -4412,127 +4412,127 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.09572337964202461</v>
+        <v>0.09624850713522233</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2096107458157689</v>
+        <v>-0.2085693173107718</v>
       </c>
       <c r="D31" t="n">
-        <v>0.179782528478993</v>
+        <v>0.1824906929407853</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1391716384486949</v>
+        <v>-0.145316873842458</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1269464255640359</v>
+        <v>-0.1140072907789972</v>
       </c>
       <c r="G31" t="n">
-        <v>0.03365039068328456</v>
+        <v>0.03769024614647229</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3460197529668707</v>
+        <v>0.3441900678803508</v>
       </c>
       <c r="I31" t="n">
-        <v>0.09304719206963938</v>
+        <v>0.09791431707114294</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02867853363680355</v>
+        <v>0.02894612754398875</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.03867372274704308</v>
+        <v>-0.03825457183153315</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.0645376542675738</v>
+        <v>-0.06526310468093068</v>
       </c>
       <c r="M31" t="n">
-        <v>0.192330735339221</v>
+        <v>0.1991399894904115</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.1390863465178888</v>
+        <v>-0.1307476542486342</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.08529881287071775</v>
+        <v>-0.07301010910437084</v>
       </c>
       <c r="P31" t="n">
-        <v>0.1505819068548828</v>
+        <v>0.1539143820451102</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.2279278479349413</v>
+        <v>-0.2275672244663999</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1343220968181598</v>
+        <v>0.1361512714017194</v>
       </c>
       <c r="S31" t="n">
-        <v>0.03652417040529689</v>
+        <v>0.04033575609951542</v>
       </c>
       <c r="T31" t="n">
-        <v>0.03522824716649146</v>
+        <v>0.03232314163386508</v>
       </c>
       <c r="U31" t="n">
-        <v>0.102747705462976</v>
+        <v>0.1074278436428254</v>
       </c>
       <c r="V31" t="n">
-        <v>0.1324035021483624</v>
+        <v>0.1328231813714136</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.1949239851486392</v>
+        <v>-0.1944497091034076</v>
       </c>
       <c r="X31" t="n">
-        <v>0.04533528842707488</v>
+        <v>0.04234394806968617</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.1945505733683307</v>
+        <v>-0.1944371434677352</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.02167677344096534</v>
+        <v>0.02152152449589036</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.07437512014852765</v>
+        <v>0.07525520142556504</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.006677145075153717</v>
+        <v>0.00683509274251658</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.04873498650846456</v>
+        <v>0.04948254208677892</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.01189534024602982</v>
+        <v>0.01194875413812558</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.02685659923247055</v>
+        <v>-0.0269181864675567</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.01123417945435451</v>
+        <v>-0.00929472444215855</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.1689679548154286</v>
+        <v>-0.164672309649995</v>
       </c>
       <c r="AH31" t="n">
-        <v>-0.005638921771443711</v>
+        <v>-0.01240703221964735</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.5703792549557233</v>
+        <v>-0.5695685598473204</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.2691438784978752</v>
+        <v>0.2716649328747284</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.1476761950685989</v>
+        <v>0.1612920106938679</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.1424482733192285</v>
+        <v>-0.130187686549232</v>
       </c>
       <c r="AM31" t="n">
-        <v>-0.01915040893576118</v>
+        <v>-0.01944037321235277</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.004007220267052897</v>
+        <v>0.004693684986389833</v>
       </c>
       <c r="AO31" t="n">
-        <v>-0.001249993737725322</v>
+        <v>-0.001278408655714647</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.0006153087507730839</v>
+        <v>0.0006888572887372066</v>
       </c>
     </row>
     <row r="32">
@@ -4542,127 +4542,127 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0083443797526909</v>
+        <v>0.008033458821502481</v>
       </c>
       <c r="C32" t="n">
-        <v>0.06741152249373915</v>
+        <v>0.06733986684792119</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.03818423950404209</v>
+        <v>-0.03894564304691703</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06551930109886066</v>
+        <v>0.06532439619442008</v>
       </c>
       <c r="F32" t="n">
-        <v>0.03529252127255082</v>
+        <v>0.03564509802124152</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.02936140459912215</v>
+        <v>-0.03053624624930214</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.008418370183430321</v>
+        <v>-0.01012167956539103</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2144351870313976</v>
+        <v>0.2144315786693657</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2737542945239022</v>
+        <v>-0.273184257287977</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7143004435617935</v>
+        <v>0.716340170524035</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.1275746831549295</v>
+        <v>-0.1215877485294712</v>
       </c>
       <c r="M32" t="n">
-        <v>0.3794928203525511</v>
+        <v>0.3686236575588296</v>
       </c>
       <c r="N32" t="n">
-        <v>0.1309933867667069</v>
+        <v>0.1125565859327683</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.2988155875314462</v>
+        <v>-0.3153592932783816</v>
       </c>
       <c r="P32" t="n">
-        <v>0.09674629453414178</v>
+        <v>0.09609912737789048</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.04180736019219938</v>
+        <v>-0.04019386841026176</v>
       </c>
       <c r="R32" t="n">
-        <v>0.03843489538287809</v>
+        <v>0.03682996783556208</v>
       </c>
       <c r="S32" t="n">
-        <v>0.03974596218785093</v>
+        <v>0.04173756568763543</v>
       </c>
       <c r="T32" t="n">
-        <v>0.08826508358083909</v>
+        <v>0.08600248303370787</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.1636086894522252</v>
+        <v>-0.1690684121253956</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.08564354074790383</v>
+        <v>-0.08245319276757937</v>
       </c>
       <c r="W32" t="n">
-        <v>0.1347834128963492</v>
+        <v>0.1365793550483205</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.03730230877873075</v>
+        <v>-0.03583446174433304</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.04379258025765767</v>
+        <v>0.04296634536187159</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.1021075545632412</v>
+        <v>-0.1029261253638876</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.02428340458112491</v>
+        <v>-0.02455791612163951</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.02212617835379332</v>
+        <v>-0.02330579921976347</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.01491266131894769</v>
+        <v>-0.01395981749261221</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.001164441809655371</v>
+        <v>0.0005377210078990922</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.01178879758224237</v>
+        <v>-0.01185802895539782</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.004531113549316138</v>
+        <v>0.005349295016303553</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.0002478347218066996</v>
+        <v>0.0008656597223617072</v>
       </c>
       <c r="AH32" t="n">
-        <v>-0.008088092070002748</v>
+        <v>-0.008238697463127654</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.002544296475052692</v>
+        <v>0.002527609157204091</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-0.0004426097989244272</v>
+        <v>-0.001081862678629092</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.005748925653142328</v>
+        <v>0.005626507758156668</v>
       </c>
       <c r="AL32" t="n">
-        <v>-0.005773368898127523</v>
+        <v>-0.006283939215049169</v>
       </c>
       <c r="AM32" t="n">
-        <v>-0.00247246799305134</v>
+        <v>-0.002389376409416094</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.000760801127214905</v>
+        <v>0.0004531037121881234</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.0002790781657685717</v>
+        <v>0.0002971262615448994</v>
       </c>
       <c r="AP32" t="n">
-        <v>8.450049064527843e-05</v>
+        <v>7.99537329588093e-05</v>
       </c>
     </row>
     <row r="33">
@@ -4672,127 +4672,127 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.07619495107740891</v>
+        <v>-0.0739964973842084</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2375847639454767</v>
+        <v>-0.2381393751474858</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2199690270269599</v>
+        <v>-0.2212417235508968</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1786214366855881</v>
+        <v>-0.1771977754719443</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0189985395734959</v>
+        <v>0.01505515948929034</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.09813985128352808</v>
+        <v>-0.09668124351500459</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1479337146829277</v>
+        <v>-0.1477522139957466</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.06337572632945283</v>
+        <v>-0.06485690767553266</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2436356350854433</v>
+        <v>0.2440931646709613</v>
       </c>
       <c r="K33" t="n">
-        <v>0.07173381137008553</v>
+        <v>0.07144457747123124</v>
       </c>
       <c r="L33" t="n">
-        <v>0.05652910379152459</v>
+        <v>0.05721819324265473</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0003987097099814491</v>
+        <v>-0.004035678392514978</v>
       </c>
       <c r="N33" t="n">
-        <v>0.03394845635757852</v>
+        <v>0.009660006028595477</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.1765715000828615</v>
+        <v>-0.1772663198694781</v>
       </c>
       <c r="P33" t="n">
-        <v>0.07195602370533996</v>
+        <v>0.0717454662707244</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.09906856612856083</v>
+        <v>0.09704512431893979</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.09234571753078685</v>
+        <v>-0.08855466811564941</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.03752755490053356</v>
+        <v>-0.03809279230740935</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3958195177688876</v>
+        <v>0.4000711907798213</v>
       </c>
       <c r="U33" t="n">
-        <v>0.09397694742070646</v>
+        <v>0.08306372782062584</v>
       </c>
       <c r="V33" t="n">
-        <v>0.1102779545557541</v>
+        <v>0.1203834074382065</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.117999483096032</v>
+        <v>-0.1101229976860259</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.06355971351256544</v>
+        <v>-0.06312382152031047</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.02727657837531001</v>
+        <v>0.02673966087836386</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.02221785291625496</v>
+        <v>0.02200903198657907</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.006244293377137286</v>
+        <v>0.006249447094162595</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.01580216148152858</v>
+        <v>-0.01630229880856456</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.03348730408182078</v>
+        <v>-0.03314006299763128</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.01583932047487704</v>
+        <v>-0.01640369016298229</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.004637441522219814</v>
+        <v>0.004518982573699436</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.003455983912519102</v>
+        <v>0.003775794859680021</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.01602699846257657</v>
+        <v>0.01694367945988395</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.01924479143250281</v>
+        <v>-0.01919756824194226</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.005415766169453922</v>
+        <v>0.005415392049306245</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.0139434470137528</v>
+        <v>0.01316725967086245</v>
       </c>
       <c r="AK33" t="n">
-        <v>-0.0003187802338873263</v>
+        <v>-0.0001266170532445806</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.0008513390702392403</v>
+        <v>0.0003575124888267396</v>
       </c>
       <c r="AM33" t="n">
-        <v>-0.009820178477618065</v>
+        <v>-0.009908179991966776</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.001337800933550319</v>
+        <v>0.001223597425884904</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.005626627897019406</v>
+        <v>0.005690435378489741</v>
       </c>
       <c r="AP33" t="n">
-        <v>-0.7050255739163374</v>
+        <v>-0.7050164100020985</v>
       </c>
     </row>
     <row r="34">
@@ -4802,127 +4802,127 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.07639336151705191</v>
+        <v>-0.07421005371625199</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2382241475947028</v>
+        <v>-0.2387868821190186</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2208989549532589</v>
+        <v>-0.2221413754351771</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1769164216541484</v>
+        <v>-0.1754909401203877</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01899468374115955</v>
+        <v>0.01506051469476522</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.09743853786532042</v>
+        <v>-0.09599653620501571</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1472682097407959</v>
+        <v>-0.1470826604935415</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0627246155476899</v>
+        <v>-0.06419940567279971</v>
       </c>
       <c r="J34" t="n">
-        <v>0.242971944582546</v>
+        <v>0.2434169021783702</v>
       </c>
       <c r="K34" t="n">
-        <v>0.07077878194834621</v>
+        <v>0.07048064387306327</v>
       </c>
       <c r="L34" t="n">
-        <v>0.05665388727854747</v>
+        <v>0.05733851821738088</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0007883007622286528</v>
+        <v>-0.003606887582552609</v>
       </c>
       <c r="N34" t="n">
-        <v>0.03376145393172951</v>
+        <v>0.009810974231726846</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.1744254909495448</v>
+        <v>-0.1751273230247547</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0729325190965433</v>
+        <v>0.0727250465259798</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.09741688516823126</v>
+        <v>0.09540587573413377</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.09040469238617664</v>
+        <v>-0.08661979989924154</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.0362959773945488</v>
+        <v>-0.03679621392753168</v>
       </c>
       <c r="T34" t="n">
-        <v>0.3943401473270281</v>
+        <v>0.3984773662756051</v>
       </c>
       <c r="U34" t="n">
-        <v>0.09217261354648405</v>
+        <v>0.08136624190853466</v>
       </c>
       <c r="V34" t="n">
-        <v>0.1098742919074544</v>
+        <v>0.1198766834476027</v>
       </c>
       <c r="W34" t="n">
-        <v>-0.1151422411219198</v>
+        <v>-0.1072858210470246</v>
       </c>
       <c r="X34" t="n">
-        <v>-0.05933768105519212</v>
+        <v>-0.05888043880086272</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.02618308434093992</v>
+        <v>0.02559740026412517</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.02048181048396574</v>
+        <v>0.02025540559858184</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.006266447681727184</v>
+        <v>0.006272089777603192</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.01565417579505566</v>
+        <v>-0.0162261886069139</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.03288638893841034</v>
+        <v>-0.03240811741302398</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.01474310783550888</v>
+        <v>-0.01526260209614366</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.005154475067618822</v>
+        <v>0.005025097358391039</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.002606787481819341</v>
+        <v>-0.002105692419391684</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.009203438694957451</v>
+        <v>0.009945621180459226</v>
       </c>
       <c r="AH34" t="n">
-        <v>-0.01152432519962837</v>
+        <v>-0.01159502391627385</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.006255787932378522</v>
+        <v>0.00626651935241409</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.009031934448796112</v>
+        <v>0.008442258011051322</v>
       </c>
       <c r="AK34" t="n">
-        <v>-0.002462547445101559</v>
+        <v>-0.002668529093074174</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.001952482491041846</v>
+        <v>0.001355855816167273</v>
       </c>
       <c r="AM34" t="n">
-        <v>-0.00343479349626866</v>
+        <v>-0.00345855707536797</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.0007111564065600629</v>
+        <v>0.0004584436083215237</v>
       </c>
       <c r="AO34" t="n">
-        <v>-0.009988773532729193</v>
+        <v>-0.01005117971117569</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.7090052140538512</v>
+        <v>0.7090129888800567</v>
       </c>
     </row>
     <row r="35">
@@ -4932,127 +4932,127 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.08264144118814383</v>
+        <v>0.08208516356715438</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2542715701372694</v>
+        <v>0.2553019178593595</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2527364891970624</v>
+        <v>0.2512203730443965</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1132843545867348</v>
+        <v>0.1113806707591906</v>
       </c>
       <c r="F35" t="n">
-        <v>0.04467113939940242</v>
+        <v>0.04621447205676336</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1161257628721453</v>
+        <v>-0.1173124408100892</v>
       </c>
       <c r="H35" t="n">
-        <v>0.123841514735762</v>
+        <v>0.1244031895857076</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.03853846373653406</v>
+        <v>-0.035798837698033</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.02136272521877714</v>
+        <v>-0.02070508878791815</v>
       </c>
       <c r="K35" t="n">
-        <v>0.02896392060859587</v>
+        <v>0.03040390340688834</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.004258422182014466</v>
+        <v>-0.004115396360700869</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.1549265911723742</v>
+        <v>-0.1591294898595964</v>
       </c>
       <c r="N35" t="n">
-        <v>0.03369377263169286</v>
+        <v>0.01436704195352962</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.03066325662295773</v>
+        <v>-0.02963263603740114</v>
       </c>
       <c r="P35" t="n">
-        <v>-0.04819382287625319</v>
+        <v>-0.04764224406128895</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.136653677495114</v>
+        <v>-0.1389167599565988</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.137180305834417</v>
+        <v>-0.12797290777676</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.1101826933552432</v>
+        <v>-0.1106227192843424</v>
       </c>
       <c r="T35" t="n">
-        <v>0.2460407647132305</v>
+        <v>0.2469854444734695</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.02903974943833543</v>
+        <v>-0.03756522373839279</v>
       </c>
       <c r="V35" t="n">
-        <v>0.08531921599147367</v>
+        <v>0.09321284644731841</v>
       </c>
       <c r="W35" t="n">
-        <v>-0.0828194333942682</v>
+        <v>-0.07565485879326671</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.4428589705427021</v>
+        <v>-0.4429707038153812</v>
       </c>
       <c r="Y35" t="n">
-        <v>-0.00694514406836803</v>
+        <v>-0.004163680989073734</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.09336191468998792</v>
+        <v>0.09472156788424445</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.02335208404531066</v>
+        <v>-0.02259705608834044</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.08393916767623055</v>
+        <v>-0.08394996868921301</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.08881645871826313</v>
+        <v>0.08937164225138458</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.02276472890289535</v>
+        <v>-0.02348731000345258</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.001457685571993628</v>
+        <v>0.001825840678544744</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.01338826352339429</v>
+        <v>-0.01240305841839013</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.04474464093020067</v>
+        <v>0.04638569151060633</v>
       </c>
       <c r="AH35" t="n">
-        <v>-0.01016077247166605</v>
+        <v>-0.009888191708010568</v>
       </c>
       <c r="AI35" t="n">
-        <v>-0.0001034917038091599</v>
+        <v>-4.808628107216741e-05</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.03066593370466311</v>
+        <v>0.02912160423386457</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.008266501049096302</v>
+        <v>0.007348263008551929</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.02027917790995101</v>
+        <v>0.02000967698157043</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.01827890548626967</v>
+        <v>0.01778527611165524</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.001085801460678747</v>
+        <v>0.000513640829558066</v>
       </c>
       <c r="AO35" t="n">
-        <v>-0.6630901052539837</v>
+        <v>-0.6631491001110422</v>
       </c>
       <c r="AP35" t="n">
-        <v>-0.00482036743171909</v>
+        <v>-0.00487663033616172</v>
       </c>
     </row>
     <row r="36">
@@ -5062,127 +5062,127 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.09758799370337241</v>
+        <v>0.09690313338763866</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2689174371853911</v>
+        <v>0.2699998433474933</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2447504439364183</v>
+        <v>0.2431491574219906</v>
       </c>
       <c r="E36" t="n">
-        <v>0.04211388980663328</v>
+        <v>0.04143723601762435</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.07751877946146313</v>
+        <v>-0.07565419558895066</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0250846861022728</v>
+        <v>0.02464691461819584</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0692481394466677</v>
+        <v>0.07075349242851231</v>
       </c>
       <c r="I36" t="n">
-        <v>0.04759027025907121</v>
+        <v>0.05034916315325424</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.09682495998072041</v>
+        <v>-0.09645427622282848</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.002637727460963812</v>
+        <v>-0.0008344610637565179</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.0117299509119914</v>
+        <v>-0.01132395728468344</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.07758101333645365</v>
+        <v>-0.07944910562566498</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.002792966373674168</v>
+        <v>-0.006659779503967002</v>
       </c>
       <c r="O36" t="n">
-        <v>0.08131350908030371</v>
+        <v>0.08571294783933843</v>
       </c>
       <c r="P36" t="n">
-        <v>0.07479456396810366</v>
+        <v>0.07462043678041784</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.09181073994903161</v>
+        <v>0.08899482335200938</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.1250955168410541</v>
+        <v>-0.1173117549395087</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.03857885973005023</v>
+        <v>-0.0382171090194352</v>
       </c>
       <c r="T36" t="n">
-        <v>0.282031541704292</v>
+        <v>0.2823374785879418</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.01035341803477448</v>
+        <v>-0.01475369624894863</v>
       </c>
       <c r="V36" t="n">
-        <v>0.1686210929267655</v>
+        <v>0.1748079329584017</v>
       </c>
       <c r="W36" t="n">
-        <v>-0.04678559953632443</v>
+        <v>-0.03580893053506767</v>
       </c>
       <c r="X36" t="n">
-        <v>-0.4168001972629903</v>
+        <v>-0.4163673904132402</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.006344266795465346</v>
+        <v>0.008139453903425457</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.1068823106906487</v>
+        <v>0.1083613322782243</v>
       </c>
       <c r="AA36" t="n">
-        <v>-0.03222354387229815</v>
+        <v>-0.03187082903503589</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.07059733513128208</v>
+        <v>-0.07104614569818826</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.06639630843013926</v>
+        <v>0.06711168635869058</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.03408082338619928</v>
+        <v>-0.0349985709711063</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.01453416884160812</v>
+        <v>0.01472024689142049</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.008207734372498348</v>
+        <v>-0.007198567627713893</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.02221512474631059</v>
+        <v>0.02359058504115753</v>
       </c>
       <c r="AH36" t="n">
-        <v>-0.01969220324009508</v>
+        <v>-0.01974554550173142</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.01153801277981541</v>
+        <v>0.01164175069354224</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.02459052984786897</v>
+        <v>0.02286263308367793</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.02750686099196314</v>
+        <v>0.02784008270032783</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.0102446171476691</v>
+        <v>0.01170848674650833</v>
       </c>
       <c r="AM36" t="n">
-        <v>-0.0470743282573195</v>
+        <v>-0.04664425539492453</v>
       </c>
       <c r="AN36" t="n">
-        <v>-0.03432110967524241</v>
+        <v>-0.03391301457668774</v>
       </c>
       <c r="AO36" t="n">
-        <v>0.6900428791386277</v>
+        <v>0.6900735850409466</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.01020599747266258</v>
+        <v>0.01026962641468939</v>
       </c>
     </row>
     <row r="37">
@@ -5192,127 +5192,127 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.05056361171612819</v>
+        <v>0.05009198323917891</v>
       </c>
       <c r="C37" t="n">
-        <v>0.07246202501319157</v>
+        <v>0.07271411790882967</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0138966269404073</v>
+        <v>0.01352005214035604</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.1608229806911856</v>
+        <v>-0.1581300971796623</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.3008905038465975</v>
+        <v>-0.3000358245059948</v>
       </c>
       <c r="G37" t="n">
-        <v>0.333249214984444</v>
+        <v>0.3350608433646034</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1239219248840904</v>
+        <v>-0.1215168314503649</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2104392913216975</v>
+        <v>0.2108463710065426</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1854305308846911</v>
+        <v>-0.1861043316328853</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.07772234304888261</v>
+        <v>-0.07671584771919063</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.0130730087281267</v>
+        <v>-0.01242864362701024</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1703049215990168</v>
+        <v>0.1756077218673744</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.08513059863311041</v>
+        <v>-0.04986634254186036</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2669375016785741</v>
+        <v>0.2753415472099255</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2924710345295872</v>
+        <v>0.2908818580514456</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.5435600687568667</v>
+        <v>0.542199675045653</v>
       </c>
       <c r="R37" t="n">
-        <v>0.01907304008296672</v>
+        <v>0.016538902333046</v>
       </c>
       <c r="S37" t="n">
-        <v>0.1654068938089775</v>
+        <v>0.1675730203489603</v>
       </c>
       <c r="T37" t="n">
-        <v>0.1191650079543756</v>
+        <v>0.1174751020057302</v>
       </c>
       <c r="U37" t="n">
-        <v>0.02872703766029874</v>
+        <v>0.03717598876757526</v>
       </c>
       <c r="V37" t="n">
-        <v>0.1978704376179792</v>
+        <v>0.1955758200418581</v>
       </c>
       <c r="W37" t="n">
-        <v>0.07453215276774612</v>
+        <v>0.08430663535072613</v>
       </c>
       <c r="X37" t="n">
-        <v>0.03183544203531304</v>
+        <v>0.0333759518569725</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.0499642635412425</v>
+        <v>0.0478041026050949</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.03708709629196418</v>
+        <v>0.03726923478175156</v>
       </c>
       <c r="AA37" t="n">
-        <v>-0.02599530475319412</v>
+        <v>-0.02669540773357332</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.01364120004111887</v>
+        <v>0.01251006768039901</v>
       </c>
       <c r="AC37" t="n">
-        <v>-0.01869711398902782</v>
+        <v>-0.01785799279530299</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.01663743603192009</v>
+        <v>-0.0172470304893565</v>
       </c>
       <c r="AE37" t="n">
-        <v>-0.01070064714375746</v>
+        <v>-0.01101670917452834</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.009326214897238332</v>
+        <v>-0.008226546803254778</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.02238390453407991</v>
+        <v>-0.02325831700288618</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.02868303183821597</v>
+        <v>0.02828346994485447</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.0001283552256140248</v>
+        <v>6.258509919419104e-05</v>
       </c>
       <c r="AJ37" t="n">
-        <v>-0.01060514743002145</v>
+        <v>-0.01025862138619755</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.002238242524160985</v>
+        <v>0.001866655417472442</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.002173066804239476</v>
+        <v>-0.002689765854191451</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.01469766673959977</v>
+        <v>0.01462738383055412</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.01414860426180929</v>
+        <v>0.01387680173964102</v>
       </c>
       <c r="AO37" t="n">
-        <v>-0.2826598404589494</v>
+        <v>-0.2826060619120007</v>
       </c>
       <c r="AP37" t="n">
-        <v>-0.003738676566590987</v>
+        <v>-0.003761441086382688</v>
       </c>
     </row>
     <row r="38">
@@ -5322,127 +5322,127 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.09031959861008107</v>
+        <v>-0.08894471225135561</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1430091862911232</v>
+        <v>-0.1435298284526627</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.05206551970506886</v>
+        <v>-0.05181102214949315</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1542809263270104</v>
+        <v>0.1542390859512746</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3794371625508381</v>
+        <v>0.3832603977873476</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.05392971555431743</v>
+        <v>-0.05601608680366259</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3316826024425713</v>
+        <v>0.3273691119107449</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1933668725229558</v>
+        <v>-0.1938741385464251</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.1791515310720371</v>
+        <v>-0.1782531434761288</v>
       </c>
       <c r="K38" t="n">
-        <v>0.03609588981329041</v>
+        <v>0.03611511492176881</v>
       </c>
       <c r="L38" t="n">
-        <v>0.02934913220080354</v>
+        <v>0.0291306569293616</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.05691307682018327</v>
+        <v>-0.05530725377682171</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.01397473293921159</v>
+        <v>-0.004248515548722202</v>
       </c>
       <c r="O38" t="n">
-        <v>0.101812945872863</v>
+        <v>0.1048728389024868</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1833401697169055</v>
+        <v>0.1823761783789777</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.2218457223725301</v>
+        <v>0.2208988730722485</v>
       </c>
       <c r="R38" t="n">
-        <v>0.005954747408333299</v>
+        <v>0.005059337889058964</v>
       </c>
       <c r="S38" t="n">
-        <v>0.05936633022583408</v>
+        <v>0.05995459576715451</v>
       </c>
       <c r="T38" t="n">
-        <v>0.08210278813818857</v>
+        <v>0.08226987748002745</v>
       </c>
       <c r="U38" t="n">
-        <v>0.04704103779294511</v>
+        <v>0.05071301871539544</v>
       </c>
       <c r="V38" t="n">
-        <v>0.0975582267527208</v>
+        <v>0.09521633918890966</v>
       </c>
       <c r="W38" t="n">
-        <v>0.0690499492476726</v>
+        <v>0.074277168219194</v>
       </c>
       <c r="X38" t="n">
-        <v>0.04090046478535161</v>
+        <v>0.04187534804823358</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.03526151628069368</v>
+        <v>0.0331592921738531</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.009867228581992273</v>
+        <v>0.009514017135787648</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.001685144086184713</v>
+        <v>0.001047274852648267</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.01288052128306321</v>
+        <v>-0.01503648889868514</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.1412805316995141</v>
+        <v>0.1415414876806304</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.6762980312461051</v>
+        <v>0.6760639436583131</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.0292498163112041</v>
+        <v>-0.02882226798501483</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.06813567179751509</v>
+        <v>0.06627202954685121</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.0690558436466117</v>
+        <v>0.0714091116771888</v>
       </c>
       <c r="AH38" t="n">
-        <v>-0.03704298564818321</v>
+        <v>-0.03613330219002074</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.008209005567289892</v>
+        <v>-0.008048010710552082</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.002704029350793105</v>
+        <v>0.0009816179919697517</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.00443388999685893</v>
+        <v>0.0031827648720547</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.02328637171429039</v>
+        <v>0.02317997536081362</v>
       </c>
       <c r="AM38" t="n">
-        <v>-0.005764586905565134</v>
+        <v>-0.00618364420480174</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.008487577648673502</v>
+        <v>0.008856031895612654</v>
       </c>
       <c r="AO38" t="n">
-        <v>0.001357516961175681</v>
+        <v>0.001380045062068531</v>
       </c>
       <c r="AP38" t="n">
-        <v>-0.0002127751103845747</v>
+        <v>-0.0002611122265796238</v>
       </c>
     </row>
     <row r="39">
@@ -5452,127 +5452,127 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.04464615846984991</v>
+        <v>0.04308605366712404</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1249765282809418</v>
+        <v>0.1250276359558951</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1246835367976359</v>
+        <v>0.125814139218408</v>
       </c>
       <c r="E39" t="n">
-        <v>0.226865976053811</v>
+        <v>0.2228179445587042</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.01731884327923807</v>
+        <v>-0.0163544079055176</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.1815336311348268</v>
+        <v>-0.1838893354358688</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0551702763747703</v>
+        <v>0.05683881230158665</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.00304166758550403</v>
+        <v>0.001321202742243454</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4979049183763979</v>
+        <v>0.4984019697956051</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1549357225535974</v>
+        <v>0.1542622073951471</v>
       </c>
       <c r="L39" t="n">
-        <v>0.05504807115940134</v>
+        <v>0.05594633241760873</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1122221079934155</v>
+        <v>0.1125628208641313</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.01116127364031304</v>
+        <v>0.001126693301009238</v>
       </c>
       <c r="O39" t="n">
-        <v>0.06607848135258909</v>
+        <v>0.06660693122199797</v>
       </c>
       <c r="P39" t="n">
-        <v>0.07397933242680811</v>
+        <v>0.07314778804071104</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.05811865341726515</v>
+        <v>0.05626924367262478</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.3044703326547727</v>
+        <v>-0.3247813556570143</v>
       </c>
       <c r="S39" t="n">
-        <v>0.6703272102362631</v>
+        <v>0.660506679635219</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.1407335823703741</v>
+        <v>-0.1395535511711676</v>
       </c>
       <c r="U39" t="n">
-        <v>0.1048243396819367</v>
+        <v>0.1126921943224525</v>
       </c>
       <c r="V39" t="n">
-        <v>0.04120665138751128</v>
+        <v>0.03479848754497417</v>
       </c>
       <c r="W39" t="n">
-        <v>0.02699794782752712</v>
+        <v>0.02648186146957847</v>
       </c>
       <c r="X39" t="n">
-        <v>0.02223073149975149</v>
+        <v>0.02185922290428546</v>
       </c>
       <c r="Y39" t="n">
-        <v>-0.02488695869866121</v>
+        <v>-0.02499875571130638</v>
       </c>
       <c r="Z39" t="n">
-        <v>-0.01305843030817964</v>
+        <v>-0.01306701072543875</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.0264632903380626</v>
+        <v>0.02645326024137195</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.01892280098913345</v>
+        <v>0.01928397871670021</v>
       </c>
       <c r="AC39" t="n">
-        <v>-0.01537987144881734</v>
+        <v>-0.01567227702906271</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.01391283623768573</v>
+        <v>-0.01366075411831799</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.002849983341315651</v>
+        <v>0.002819917208855909</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.007886470861052156</v>
+        <v>0.007589948288913954</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.005061439045093967</v>
+        <v>0.005115964509826184</v>
       </c>
       <c r="AH39" t="n">
-        <v>-0.00393680242490051</v>
+        <v>-0.003760557221213929</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0.003190748835925714</v>
+        <v>-0.003299749828952876</v>
       </c>
       <c r="AJ39" t="n">
-        <v>-0.001403386768998624</v>
+        <v>-0.001328212877235959</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.005019153768620221</v>
+        <v>-0.00504486648680786</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.580602171925787e-06</v>
+        <v>-0.0002285632463656225</v>
       </c>
       <c r="AM39" t="n">
-        <v>-0.0004447473755786535</v>
+        <v>-0.0005046228215313982</v>
       </c>
       <c r="AN39" t="n">
-        <v>0.001553232890154217</v>
+        <v>0.001535649594453445</v>
       </c>
       <c r="AO39" t="n">
-        <v>-0.000447022292719366</v>
+        <v>-0.0004364347487037723</v>
       </c>
       <c r="AP39" t="n">
-        <v>-8.878221921034915e-05</v>
+        <v>-9.048837252117273e-05</v>
       </c>
     </row>
     <row r="40">
@@ -5582,127 +5582,127 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.09190284243748301</v>
+        <v>-0.09052876719353559</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1345506546219009</v>
+        <v>-0.135049306793691</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.04123246800146031</v>
+        <v>-0.04095459642697323</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1612365565359192</v>
+        <v>0.1613864737003619</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3837431401971308</v>
+        <v>0.3877905283029835</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.03952055046043583</v>
+        <v>-0.04170982762647456</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3398209210431388</v>
+        <v>0.3353607490567018</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1848516244511198</v>
+        <v>-0.1855132852715197</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.2093257973837889</v>
+        <v>-0.2084174897724579</v>
       </c>
       <c r="K40" t="n">
-        <v>0.03010000601746919</v>
+        <v>0.03016036554525931</v>
       </c>
       <c r="L40" t="n">
-        <v>0.062434253452727</v>
+        <v>0.06228183834857601</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.05147270499012612</v>
+        <v>-0.04997659063960055</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.01567108325649237</v>
+        <v>-0.006967090193470254</v>
       </c>
       <c r="O40" t="n">
-        <v>0.09257223356922079</v>
+        <v>0.09573187101229527</v>
       </c>
       <c r="P40" t="n">
-        <v>0.1584968497564845</v>
+        <v>0.1576467000662891</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.2010386238364767</v>
+        <v>0.2002003895116021</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.003014753169025149</v>
+        <v>-0.003745875333962662</v>
       </c>
       <c r="S40" t="n">
-        <v>0.03419414848265694</v>
+        <v>0.03413904806161809</v>
       </c>
       <c r="T40" t="n">
-        <v>0.05151572928662413</v>
+        <v>0.05223551926984572</v>
       </c>
       <c r="U40" t="n">
-        <v>0.05694439447558836</v>
+        <v>0.05958791362863115</v>
       </c>
       <c r="V40" t="n">
-        <v>0.05262620910197682</v>
+        <v>0.04981750294162753</v>
       </c>
       <c r="W40" t="n">
-        <v>0.02812296147407948</v>
+        <v>0.02997865144189607</v>
       </c>
       <c r="X40" t="n">
-        <v>0.02278469458590091</v>
+        <v>0.02275985286733111</v>
       </c>
       <c r="Y40" t="n">
-        <v>-0.02398860124631168</v>
+        <v>-0.02436818054817676</v>
       </c>
       <c r="Z40" t="n">
-        <v>-0.04847790487980322</v>
+        <v>-0.04855493924560491</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.05678349961662971</v>
+        <v>0.05664691087911743</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.06579191218046943</v>
+        <v>0.06731413351316796</v>
       </c>
       <c r="AC40" t="n">
-        <v>-0.1899737262795756</v>
+        <v>-0.1899169048067519</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.6754948117291935</v>
+        <v>-0.675452381084702</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.02980729151065216</v>
+        <v>0.02914152207668388</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.04201314901704106</v>
+        <v>-0.03994402872817004</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.04318498812845353</v>
+        <v>-0.04541069690911123</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.04436722879137327</v>
+        <v>0.04409650469271503</v>
       </c>
       <c r="AI40" t="n">
-        <v>-0.01293890096160134</v>
+        <v>-0.01321846564514496</v>
       </c>
       <c r="AJ40" t="n">
-        <v>-0.01679133397369489</v>
+        <v>-0.01553723533072267</v>
       </c>
       <c r="AK40" t="n">
-        <v>-0.02492848639657794</v>
+        <v>-0.0250977344615947</v>
       </c>
       <c r="AL40" t="n">
-        <v>-0.00675239826423061</v>
+        <v>-0.008776895788619307</v>
       </c>
       <c r="AM40" t="n">
-        <v>-4.040944456406594e-05</v>
+        <v>0.000225994383245407</v>
       </c>
       <c r="AN40" t="n">
-        <v>-0.001587328013628316</v>
+        <v>-0.002169722232616137</v>
       </c>
       <c r="AO40" t="n">
-        <v>-0.006103513133252907</v>
+        <v>-0.006113904807714537</v>
       </c>
       <c r="AP40" t="n">
-        <v>-0.000719001449550248</v>
+        <v>-0.0006795980724207621</v>
       </c>
     </row>
     <row r="41">
@@ -5712,127 +5712,127 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.04547812901538374</v>
+        <v>0.04362993280198339</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1105221465706525</v>
+        <v>0.1103965971047534</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1152614704522554</v>
+        <v>0.1169672875046517</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2212832401268396</v>
+        <v>0.217082651874657</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.02144636144891671</v>
+        <v>-0.01957509840910236</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1601988172078137</v>
+        <v>-0.1623244306957399</v>
       </c>
       <c r="H41" t="n">
-        <v>0.07416695158791449</v>
+        <v>0.07514540018004062</v>
       </c>
       <c r="I41" t="n">
-        <v>0.01847931167764165</v>
+        <v>0.02231066389193242</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5064981432193474</v>
+        <v>0.5072357279944573</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1704985124148677</v>
+        <v>0.1696272842489413</v>
       </c>
       <c r="L41" t="n">
-        <v>0.07447446931552107</v>
+        <v>0.07552428087324874</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1713600566622359</v>
+        <v>0.174781111392438</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.02330756044826722</v>
+        <v>0.005498976360059742</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1527209382274306</v>
+        <v>0.1524829799520827</v>
       </c>
       <c r="P41" t="n">
-        <v>0.06050903556516197</v>
+        <v>0.05918124167712642</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.3067944020605354</v>
+        <v>0.3087218008111364</v>
       </c>
       <c r="R41" t="n">
-        <v>0.4494739636496061</v>
+        <v>0.4598642881088578</v>
       </c>
       <c r="S41" t="n">
-        <v>-0.4870869780437859</v>
+        <v>-0.4755590341995514</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.08465492179381282</v>
+        <v>-0.08762760721029914</v>
       </c>
       <c r="U41" t="n">
-        <v>-0.002333690759080246</v>
+        <v>0.00461889485247003</v>
       </c>
       <c r="V41" t="n">
-        <v>0.04046664514997858</v>
+        <v>0.03539063462035175</v>
       </c>
       <c r="W41" t="n">
-        <v>0.02941703837728262</v>
+        <v>0.02943517637564357</v>
       </c>
       <c r="X41" t="n">
-        <v>-0.001385579944541972</v>
+        <v>-0.001372718326440823</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.0003657132240468455</v>
+        <v>0.0004506236195062851</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.005929963174783833</v>
+        <v>-0.0057124301341643</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01067867490327061</v>
+        <v>0.01064588513579114</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.004396520948006858</v>
+        <v>0.00472006723092655</v>
       </c>
       <c r="AC41" t="n">
-        <v>-0.009927300459194391</v>
+        <v>-0.01024837647364163</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.006378162923806569</v>
+        <v>-0.006015207168214676</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.002880242442122905</v>
+        <v>0.002903146983491834</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.00564011238044834</v>
+        <v>0.005272536647889407</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.002879441549091334</v>
+        <v>0.002786276713603409</v>
       </c>
       <c r="AH41" t="n">
-        <v>-0.001330061862495804</v>
+        <v>-0.001214194808059235</v>
       </c>
       <c r="AI41" t="n">
-        <v>-0.001165049106483902</v>
+        <v>-0.001141353390272464</v>
       </c>
       <c r="AJ41" t="n">
-        <v>-0.0013746695410511</v>
+        <v>-0.00130592376698146</v>
       </c>
       <c r="AK41" t="n">
-        <v>-0.001112595738383021</v>
+        <v>-0.0009967843126620121</v>
       </c>
       <c r="AL41" t="n">
-        <v>-0.001010183684925085</v>
+        <v>-0.0009266052223507819</v>
       </c>
       <c r="AM41" t="n">
-        <v>-0.002373937727744113</v>
+        <v>-0.002410715376724921</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.0009356468114548363</v>
+        <v>0.0009845682848172613</v>
       </c>
       <c r="AO41" t="n">
-        <v>6.930604312692174e-05</v>
+        <v>6.677020085115316e-05</v>
       </c>
       <c r="AP41" t="n">
-        <v>6.821571153160452e-06</v>
+        <v>9.692362829786279e-06</v>
       </c>
     </row>
     <row r="42">
@@ -5842,127 +5842,127 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.02377945617614426</v>
+        <v>-0.02421135664022382</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01436837524776152</v>
+        <v>0.01404087636465686</v>
       </c>
       <c r="D42" t="n">
-        <v>0.03745833122452591</v>
+        <v>0.03841863518548858</v>
       </c>
       <c r="E42" t="n">
-        <v>0.02771509518914151</v>
+        <v>0.027266850254207</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.04611454044060491</v>
+        <v>-0.04327201558617038</v>
       </c>
       <c r="G42" t="n">
-        <v>0.141526392952952</v>
+        <v>0.1411188807512432</v>
       </c>
       <c r="H42" t="n">
-        <v>0.04430546406951589</v>
+        <v>0.04323648281757327</v>
       </c>
       <c r="I42" t="n">
-        <v>0.07467258976591978</v>
+        <v>0.07379731123703408</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.08579114038068952</v>
+        <v>-0.08584307226082935</v>
       </c>
       <c r="K42" t="n">
-        <v>0.03204995377333153</v>
+        <v>0.02968891006574032</v>
       </c>
       <c r="L42" t="n">
-        <v>0.9627825084181991</v>
+        <v>0.9633918030791409</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1108414857556136</v>
+        <v>0.106835544871267</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.008074822122023959</v>
+        <v>-0.0238216227639889</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.08116017576123231</v>
+        <v>-0.0793800716570351</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.05194520719576134</v>
+        <v>-0.05183753932599532</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.08163293458303227</v>
+        <v>-0.08259197832325826</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.01708488508946227</v>
+        <v>-0.0157104871634375</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.007047913752737485</v>
+        <v>-0.007044162413871911</v>
       </c>
       <c r="T42" t="n">
-        <v>0.01183525381021848</v>
+        <v>0.01171834325229694</v>
       </c>
       <c r="U42" t="n">
-        <v>-0.004611737020359931</v>
+        <v>-0.005728036776681048</v>
       </c>
       <c r="V42" t="n">
-        <v>-0.02700354303095583</v>
+        <v>-0.02772970949903849</v>
       </c>
       <c r="W42" t="n">
-        <v>0.006393440766846596</v>
+        <v>0.004835730960736412</v>
       </c>
       <c r="X42" t="n">
-        <v>-0.001642904953930132</v>
+        <v>-0.0016969942053921</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.0002059393751227979</v>
+        <v>0.0001407247975427212</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.01954721902328531</v>
+        <v>0.01960586231830599</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.02726180856587307</v>
+        <v>0.02749294434709052</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.01082973790794049</v>
+        <v>-0.01062585171860552</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.001394382183301571</v>
+        <v>0.001281479751141883</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.03052561873980713</v>
+        <v>0.03068409759750185</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.01397736725447323</v>
+        <v>-0.01395275666564225</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.002178081079379491</v>
+        <v>-0.002493516332826711</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.005911109358167836</v>
+        <v>0.005735480387691722</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.003023064938529521</v>
+        <v>0.003267271738117289</v>
       </c>
       <c r="AI42" t="n">
-        <v>-0.002860953379586645</v>
+        <v>-0.002839817277247481</v>
       </c>
       <c r="AJ42" t="n">
-        <v>-0.002354503172142877</v>
+        <v>-0.002202690854444131</v>
       </c>
       <c r="AK42" t="n">
-        <v>-0.002597748134904808</v>
+        <v>-0.002613345739733588</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.0009095251303729439</v>
+        <v>0.0009431544044702426</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.000229386387224038</v>
+        <v>0.0002165862037463023</v>
       </c>
       <c r="AN42" t="n">
-        <v>-0.0009411679658413825</v>
+        <v>-0.0008969279063941351</v>
       </c>
       <c r="AO42" t="n">
-        <v>0.002312169456901595</v>
+        <v>0.002316333886713923</v>
       </c>
       <c r="AP42" t="n">
-        <v>-0.0001612741870490958</v>
+        <v>-0.0001634437289117123</v>
       </c>
     </row>
   </sheetData>
